--- a/Excel/悖论模拟干员名单作者版.xlsx
+++ b/Excel/悖论模拟干员名单作者版.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>*maa://22880 (70.2), maa://20276 (82.73), *maa://22749 (62.5)</t>
+          <t>*maa://22880 (69.74), maa://20276 (82.73), *maa://22749 (62.5)</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>maa://28624 (91.3), maa://24957 (97.3)</t>
+          <t>maa://28624 (91.3), maa://24957 (97.37)</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="AA12" s="5" t="inlineStr">
         <is>
-          <t>maa://23669 (95.86), maa://36677 (94.87), maa://39872 (83.33)</t>
+          <t>maa://23669 (95.86), maa://36677 (94.87), maa://39872 (84.62)</t>
         </is>
       </c>
       <c r="AC12" s="4" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
-          <t>maa://22676 (91.75), *maa://22583 (74.58), *maa://22500 (55.81)</t>
+          <t>maa://22676 (91.84), *maa://22583 (74.58), *maa://22500 (55.81)</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>maa://22864 (88.37)</t>
+          <t>maa://22864 (88.46)</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>maa://39756 (92.11), maa://39875 (95.56)</t>
+          <t>maa://39756 (92.11), maa://39875 (95.65)</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="W24" s="5" t="inlineStr">
         <is>
-          <t>maa://23504 (92.86), maa://29988 (86.07), **maa://22892 (40.14), *maa://25141 (76.86), *maa://36663 (80.0), ***maa://22815 (23.08)</t>
+          <t>maa://23504 (92.88), maa://29988 (86.07), **maa://22892 (40.14), *maa://25141 (76.86), *maa://36663 (80.0), ***maa://22815 (23.08)</t>
         </is>
       </c>
       <c r="Y24" s="4" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>*maa://29063 (76.15), *maa://25311 (73.91), ***maa://22725 (4.84)</t>
+          <t>*maa://29063 (76.15), *maa://25311 (74.19), ***maa://22725 (4.84)</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AA26" s="5" t="inlineStr">
         <is>
-          <t>***maa://42235 (25.0)</t>
+          <t>**maa://42235 (40.0)</t>
         </is>
       </c>
       <c r="AC26" s="4" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>maa://24465 (90.32), maa://25725 (82.28)</t>
+          <t>maa://24465 (90.33), maa://25725 (82.28)</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="W28" s="5" t="inlineStr">
         <is>
-          <t>maa://39929 (85.64), ***maa://39723 (14.71), maa://41749 (85.71)</t>
+          <t>maa://39929 (85.64), ***maa://39723 (14.71), maa://41749 (86.67)</t>
         </is>
       </c>
       <c r="Y28" s="4" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>maa://30442 (94.23)</t>
+          <t>maa://30442 (94.34)</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>maa://41108 (89.66), maa://41238 (94.44)</t>
+          <t>maa://41108 (90.0), maa://41238 (94.44)</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>maa://41296 (97.62)</t>
+          <t>maa://41296 (97.67)</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>maa://35931 (92.44)</t>
+          <t>maa://35931 (92.48)</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>maa://27410 (95.79), maa://29661 (97.64), maa://28038 (84.62)</t>
+          <t>maa://27410 (95.81), maa://29661 (97.64), maa://28038 (84.62)</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>maa://32532 (92.27)</t>
+          <t>maa://32532 (92.31)</t>
         </is>
       </c>
     </row>

--- a/Excel/悖论模拟干员名单作者版.xlsx
+++ b/Excel/悖论模拟干员名单作者版.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="AA2" s="5" t="inlineStr">
         <is>
-          <t>maa://21246 (91.2), maa://36684 (98.63), ***maa://22731 (6.67)</t>
+          <t>maa://21246 (91.23), maa://36684 (98.63), ***maa://22731 (6.67)</t>
         </is>
       </c>
       <c r="AC2" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>*maa://22880 (69.93), maa://20276 (82.86), *maa://22749 (62.5)</t>
+          <t>*maa://22880 (69.48), maa://20276 (82.86), *maa://22749 (62.5)</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="W3" s="5" t="inlineStr">
         <is>
-          <t>maa://27396 (84.97), maa://27484 (95.74), maa://27480 (82.35)</t>
+          <t>maa://27396 (85.02), maa://27484 (95.74), maa://27480 (82.35)</t>
         </is>
       </c>
       <c r="Y3" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="AA3" s="5" t="inlineStr">
         <is>
-          <t>maa://24390 (96.08)</t>
+          <t>maa://24390 (96.15)</t>
         </is>
       </c>
       <c r="AC3" s="4" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="W4" s="5" t="inlineStr">
         <is>
-          <t>**maa://32495 (47.54), ***maa://31785 (18.75), ***maa://36683 (26.67)</t>
+          <t>**maa://32495 (47.54), ***maa://31785 (19.47), ***maa://36683 (26.67)</t>
         </is>
       </c>
       <c r="Y4" s="4" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AA6" s="5" t="inlineStr">
         <is>
-          <t>maa://22739 (91.3)</t>
+          <t>maa://22739 (91.67)</t>
         </is>
       </c>
       <c r="AC6" s="4" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AE7" s="5" t="inlineStr">
         <is>
-          <t>*maa://26191 (68.49), *maa://36671 (72.09), maa://42530 (100.0)</t>
+          <t>*maa://26191 (68.49), *maa://36671 (72.73), maa://42530 (100.0)</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="W8" s="5" t="inlineStr">
         <is>
-          <t>maa://21411 (96.03)</t>
+          <t>maa://21411 (96.04)</t>
         </is>
       </c>
       <c r="Y8" s="4" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="W10" s="5" t="inlineStr">
         <is>
-          <t>maa://22301 (97.41), maa://22726 (100.0)</t>
+          <t>maa://22301 (97.42), maa://22726 (100.0)</t>
         </is>
       </c>
       <c r="Y10" s="4" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>maa://21867 (90.0)</t>
+          <t>maa://21867 (90.07)</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AE15" s="5" t="inlineStr">
         <is>
-          <t>maa://21364 (80.61), *maa://22766 (73.0), *maa://36666 (78.46)</t>
+          <t>maa://21364 (80.68), *maa://22766 (73.0), *maa://36666 (78.46)</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AE16" s="5" t="inlineStr">
         <is>
-          <t>*maa://23911 (61.96), maa://27755 (91.78)</t>
+          <t>*maa://23911 (61.96), maa://27755 (91.89)</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>maa://24570 (96.61)</t>
+          <t>maa://24570 (96.63)</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="AA19" s="5" t="inlineStr">
         <is>
-          <t>*maa://30709 (60.8), *maa://36668 (52.17)</t>
+          <t>*maa://30709 (60.9), *maa://36668 (52.17)</t>
         </is>
       </c>
       <c r="AC19" s="4" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>maa://39756 (92.5), maa://39875 (95.83)</t>
+          <t>maa://39756 (92.55), maa://39875 (95.83)</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="W23" s="5" t="inlineStr">
         <is>
-          <t>*maa://28503 (63.33)</t>
+          <t>*maa://28503 (63.93)</t>
         </is>
       </c>
       <c r="Y23" s="4" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>maa://24368 (80.36)</t>
+          <t>maa://24368 (80.42)</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>maa://29753 (95.15)</t>
+          <t>maa://29753 (95.18)</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AA26" s="5" t="inlineStr">
         <is>
-          <t>*maa://42235 (73.68)</t>
+          <t>*maa://42235 (75.0)</t>
         </is>
       </c>
       <c r="AC26" s="4" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="W28" s="5" t="inlineStr">
         <is>
-          <t>maa://39929 (86.7), ***maa://39723 (14.71), maa://41749 (81.25)</t>
+          <t>maa://39929 (86.76), ***maa://39723 (14.71), maa://41749 (81.25)</t>
         </is>
       </c>
       <c r="Y28" s="4" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AE28" s="5" t="inlineStr">
         <is>
-          <t>maa://36660 (93.85), *maa://36701 (64.0)</t>
+          <t>maa://36660 (93.87), *maa://36701 (64.0)</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>maa://28432 (93.47), *maa://28440 (72.84), maa://31400 (100.0), *maa://28650 (66.67)</t>
+          <t>maa://28432 (93.49), *maa://28440 (72.84), maa://31400 (100.0), *maa://28650 (66.67)</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>maa://41108 (91.43), maa://41238 (94.59)</t>
+          <t>maa://41108 (91.67), maa://41238 (94.59)</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="S34" s="5" t="inlineStr">
         <is>
-          <t>maa://24526 (93.13)</t>
+          <t>maa://24526 (93.16)</t>
         </is>
       </c>
       <c r="Y34" s="4" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AE38" s="5" t="inlineStr">
         <is>
-          <t>maa://36697 (84.62)</t>
+          <t>maa://36697 (84.73)</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>maa://23278 (95.88), maa://21386 (95.63), maa://36664 (90.24)</t>
+          <t>maa://23278 (95.89), maa://21386 (95.63), maa://36664 (90.24)</t>
         </is>
       </c>
       <c r="Q40" s="4" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>maa://29768 (97.52), maa://27728 (96.0)</t>
+          <t>maa://29768 (97.54), maa://27728 (96.0)</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>maa://35931 (92.58)</t>
+          <t>maa://35931 (92.61)</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>maa://27410 (95.81), maa://29661 (97.64), maa://28038 (84.62)</t>
+          <t>maa://27410 (95.82), maa://29661 (97.64), maa://28038 (84.62)</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>maa://32534 (93.21), **maa://32434 (36.36)</t>
+          <t>maa://32534 (93.23), **maa://32434 (36.36)</t>
         </is>
       </c>
     </row>

--- a/Excel/悖论模拟干员名单作者版.xlsx
+++ b/Excel/悖论模拟干员名单作者版.xlsx
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>maa://42407 (87.5)</t>
+          <t>maa://42407 (88.89)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="S6" s="5" t="inlineStr">
         <is>
-          <t>*maa://37411 (75.0)</t>
+          <t>*maa://37411 (77.78)</t>
         </is>
       </c>
       <c r="U6" s="4" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>maa://32931 (88.89), *maa://21916 (60.34), maa://23252 (92.31), **maa://22759 (45.45), maa://37496 (100.0)</t>
+          <t>maa://32931 (87.8), *maa://21916 (60.34), maa://23252 (92.31), **maa://22759 (45.45), maa://37496 (100.0)</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="S9" s="5" t="inlineStr">
         <is>
-          <t>**maa://22866 (30.77), maa://26222 (97.3)</t>
+          <t>**maa://22866 (30.77), maa://26222 (97.37)</t>
         </is>
       </c>
       <c r="U9" s="4" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="W13" s="5" t="inlineStr">
         <is>
-          <t>*maa://34957 (76.6), *maa://22768 (53.33)</t>
+          <t>*maa://34957 (76.6), *maa://22768 (51.61)</t>
         </is>
       </c>
       <c r="Y13" s="4" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
-          <t>maa://28504 (91.67)</t>
+          <t>maa://28504 (91.84)</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>maa://31731 (95.12)</t>
+          <t>maa://31731 (95.24)</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="AE21" s="5" t="inlineStr">
         <is>
-          <t>maa://22524 (94.29), *maa://22432 (74.55)</t>
+          <t>maa://22524 (94.32), *maa://22432 (74.55)</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>*maa://29063 (76.12), *maa://25311 (74.19), ***maa://22725 (4.84)</t>
+          <t>*maa://29063 (75.56), *maa://25311 (74.19), ***maa://22725 (4.84)</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AA26" s="5" t="inlineStr">
         <is>
-          <t>*maa://42235 (76.19)</t>
+          <t>*maa://42235 (78.26)</t>
         </is>
       </c>
       <c r="AC26" s="4" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="W28" s="5" t="inlineStr">
         <is>
-          <t>maa://39929 (86.83), ***maa://39723 (14.71), maa://41749 (81.25)</t>
+          <t>maa://39929 (86.83), ***maa://39723 (14.71), maa://41749 (82.35)</t>
         </is>
       </c>
       <c r="Y28" s="4" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AE28" s="5" t="inlineStr">
         <is>
-          <t>maa://36660 (93.87), *maa://36701 (64.0)</t>
+          <t>maa://36660 (93.89), *maa://36701 (64.0)</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>maa://31694 (97.92)</t>
+          <t>maa://31694 (97.96)</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>maa://41296 (98.15)</t>
+          <t>maa://41296 (98.18)</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>maa://21280 (89.13), *maa://21239 (72.73)</t>
+          <t>maa://21280 (89.19), *maa://21239 (72.73)</t>
         </is>
       </c>
       <c r="Q37" s="4" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AE38" s="5" t="inlineStr">
         <is>
-          <t>maa://36697 (84.73)</t>
+          <t>maa://36697 (84.09)</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>**maa://35616 (37.93)</t>
+          <t>**maa://35616 (36.67)</t>
         </is>
       </c>
       <c r="Q41" s="4" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>maa://35931 (92.61)</t>
+          <t>maa://35931 (92.64)</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">

--- a/Excel/悖论模拟干员名单作者版.xlsx
+++ b/Excel/悖论模拟干员名单作者版.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>maa://24702 (94.22), maa://25390 (95.88), maa://36681 (86.84)</t>
+          <t>maa://24702 (94.22), maa://25390 (95.9), maa://36681 (87.01)</t>
         </is>
       </c>
       <c r="E2" s="1" t="n"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>maa://22742 (91.39), *maa://20791 (62.32)</t>
+          <t>maa://22742 (91.39), *maa://20791 (62.86)</t>
         </is>
       </c>
       <c r="U2" s="1" t="n"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>maa://21246 (91.32), maa://36684 (95.6), ***maa://22731 (6.67)</t>
+          <t>maa://21246 (91.32), maa://36684 (95.65), ***maa://22731 (6.67)</t>
         </is>
       </c>
       <c r="AC2" s="1" t="n"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>maa://25251 (92.39), ***maa://21730 (19.4), ***maa://39501 (15.79), *maa://36675 (60.0)</t>
+          <t>maa://25251 (92.39), ***maa://21730 (19.4), ***maa://39501 (15.0), *maa://36675 (60.0)</t>
         </is>
       </c>
       <c r="AG2" s="1" t="n"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>maa://36987 (93.62), maa://40192 (96.67), maa://39849 (88.89)</t>
+          <t>maa://36987 (93.75), maa://40192 (96.67), maa://39849 (88.89)</t>
         </is>
       </c>
       <c r="E3" s="1" t="n"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>maa://21249 (94.55), maa://26254 (95.83)</t>
+          <t>maa://21249 (94.57), maa://26254 (95.83)</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>maa://27396 (84.69), maa://27484 (96.0), maa://27480 (82.86)</t>
+          <t>maa://27396 (84.69), maa://27484 (96.04), maa://27480 (82.86)</t>
         </is>
       </c>
       <c r="Y3" s="1" t="n"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>maa://32509 (97.89), maa://27295 (83.33), maa://22754 (91.67), *maa://21746 (55.81), *maa://31008 (78.05)</t>
+          <t>maa://32509 (97.92), maa://27295 (83.33), maa://22754 (91.67), *maa://21746 (55.81), *maa://31008 (78.05)</t>
         </is>
       </c>
       <c r="U4" s="1" t="n"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>**maa://32495 (47.67), ***maa://31785 (22.22), ***maa://36683 (28.26), maa://43217 (88.89)</t>
+          <t>**maa://32495 (47.88), ***maa://31785 (22.22), ***maa://36683 (28.26), maa://43217 (88.89)</t>
         </is>
       </c>
       <c r="Y4" s="1" t="n"/>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>maa://28624 (92.94), maa://24957 (97.62)</t>
+          <t>maa://28624 (93.02), maa://24957 (97.62)</t>
         </is>
       </c>
       <c r="M7" s="1" t="n"/>
@@ -1429,7 +1429,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2024.12.08 15:46:46</t>
+          <t>更新日期：2024.12.10 13:19:52</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>*maa://21476 (71.74), **maa://39431 (44.44), *maa://37551 (57.14)</t>
+          <t>*maa://21476 (71.74), **maa://39431 (40.0), *maa://37551 (57.14)</t>
         </is>
       </c>
       <c r="E8" s="1" t="n"/>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>maa://22762 (91.76), maa://39552 (90.0)</t>
+          <t>maa://22762 (91.86), maa://39552 (90.0)</t>
         </is>
       </c>
       <c r="M9" s="1" t="n"/>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>**maa://22866 (30.77), maa://26222 (97.67)</t>
+          <t>**maa://22866 (30.19), maa://26222 (97.73)</t>
         </is>
       </c>
       <c r="U9" s="1" t="n"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>maa://28711 (86.73), ***maa://22740 (5.88), **maa://39938 (48.0), **maa://27377 (42.86), ***maa://25174 (19.05), maa://40166 (92.86)</t>
+          <t>maa://28711 (86.87), ***maa://22740 (5.88), **maa://39938 (48.0), **maa://27377 (42.86), ***maa://25174 (19.05), maa://40166 (92.86)</t>
         </is>
       </c>
       <c r="AC9" s="1" t="n"/>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>maa://27395 (95.93), maa://22755 (87.39), **maa://22756 (40.91), ***maa://21737 (10.61)</t>
+          <t>maa://27395 (95.93), maa://22755 (87.5), **maa://22756 (40.91), ***maa://21737 (10.61)</t>
         </is>
       </c>
       <c r="U10" s="1" t="n"/>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AF10" s="2" t="inlineStr">
         <is>
-          <t>*maa://25021 (53.09), *maa://22733 (59.38), maa://22761 (100.0)</t>
+          <t>*maa://25021 (53.66), *maa://22733 (59.38), maa://22761 (100.0)</t>
         </is>
       </c>
       <c r="AG10" s="1" t="n"/>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>maa://24999 (91.7), maa://36673 (92.65), maa://25001 (85.51)</t>
+          <t>maa://24999 (91.73), maa://36673 (92.65), maa://25001 (85.51)</t>
         </is>
       </c>
       <c r="E13" s="1" t="n"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>*maa://34957 (78.69), *maa://22768 (51.61)</t>
+          <t>*maa://34957 (79.03), *maa://22768 (51.61)</t>
         </is>
       </c>
       <c r="Y13" s="1" t="n"/>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>maa://30764 (88.0)</t>
+          <t>maa://30764 (88.24)</t>
         </is>
       </c>
       <c r="E14" s="1" t="n"/>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>maa://26245 (96.38), maa://21288 (96.24), maa://39841 (94.87), maa://36682 (97.37)</t>
+          <t>maa://26245 (96.43), maa://21288 (96.24), maa://39841 (94.87), maa://36682 (97.37)</t>
         </is>
       </c>
       <c r="M14" s="1" t="n"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>maa://23250 (98.61), maa://20107 (87.1), maa://22772 (100.0), **maa://22745 (50.0)</t>
+          <t>maa://23250 (98.62), maa://20107 (87.1), maa://22772 (100.0), **maa://22745 (50.0)</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n"/>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>maa://22521 (93.68), maa://42751 (100.0)</t>
+          <t>maa://22521 (93.75), maa://42751 (100.0)</t>
         </is>
       </c>
       <c r="U14" s="1" t="n"/>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>maa://37468 (88.89)</t>
+          <t>maa://37468 (89.47)</t>
         </is>
       </c>
       <c r="Y14" s="1" t="n"/>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>maa://22764 (96.83)</t>
+          <t>maa://22764 (96.88)</t>
         </is>
       </c>
       <c r="AC14" s="1" t="n"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>*maa://22743 (76.84), maa://22734 (83.9), *maa://30808 (63.93), ***maa://36048 (28.57)</t>
+          <t>*maa://22743 (76.84), maa://22734 (83.9), *maa://30808 (64.52), ***maa://36048 (28.57)</t>
         </is>
       </c>
       <c r="E15" s="1" t="n"/>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>maa://24304 (88.5), maa://21478 (91.43)</t>
+          <t>maa://24304 (88.56), maa://21478 (91.43)</t>
         </is>
       </c>
       <c r="I15" s="1" t="n"/>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AF15" s="2" t="inlineStr">
         <is>
-          <t>maa://21364 (80.59), *maa://22766 (70.64), *maa://36666 (78.05)</t>
+          <t>maa://21364 (80.59), *maa://22766 (70.64), *maa://36666 (78.31)</t>
         </is>
       </c>
       <c r="AG15" s="1" t="n"/>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>maa://21441 (96.28), maa://36679 (92.68), maa://37650 (96.88)</t>
+          <t>maa://21441 (96.28), maa://36679 (92.86), maa://37650 (96.88)</t>
         </is>
       </c>
       <c r="E16" s="1" t="n"/>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>**maa://42324 (45.83)</t>
+          <t>**maa://42324 (48.0)</t>
         </is>
       </c>
       <c r="U17" s="1" t="n"/>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>maa://24421 (90.17)</t>
+          <t>maa://24421 (90.25)</t>
         </is>
       </c>
       <c r="I18" s="1" t="n"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>maa://21917 (97.7), maa://22741 (83.33)</t>
+          <t>maa://21917 (97.73), maa://22741 (83.33)</t>
         </is>
       </c>
       <c r="Y18" s="1" t="n"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>maa://24386 (98.99)</t>
+          <t>maa://24386 (99.0)</t>
         </is>
       </c>
       <c r="U19" s="1" t="n"/>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>maa://21432 (89.73), maa://25198 (92.93), *maa://20795 (51.18), maa://36680 (96.55)</t>
+          <t>maa://21432 (89.73), maa://25198 (93.0), *maa://20795 (51.18), maa://36680 (96.55)</t>
         </is>
       </c>
       <c r="E20" s="1" t="n"/>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>maa://20110 (86.76), maa://34946 (92.31)</t>
+          <t>maa://20110 (86.76), maa://34946 (92.5)</t>
         </is>
       </c>
       <c r="Y21" s="1" t="n"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="AF21" s="2" t="inlineStr">
         <is>
-          <t>maa://22524 (94.53), *maa://22432 (76.67)</t>
+          <t>maa://22524 (94.55), *maa://22432 (76.67)</t>
         </is>
       </c>
       <c r="AG21" s="1" t="n"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>maa://27127 (86.0), *maa://22751 (73.85)</t>
+          <t>maa://27127 (85.15), *maa://22751 (73.85)</t>
         </is>
       </c>
       <c r="M22" s="1" t="n"/>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>***maa://28036 (28.36), *maa://41753 (54.55)</t>
+          <t>***maa://28036 (28.36), *maa://41753 (58.33)</t>
         </is>
       </c>
       <c r="E23" s="1" t="n"/>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>maa://29988 (86.55), maa://23504 (93.18), **maa://22892 (39.58), *maa://25141 (77.6), maa://36663 (81.54), ***maa://22815 (23.08)</t>
+          <t>maa://29988 (86.61), maa://23504 (93.19), **maa://22892 (39.58), *maa://25141 (77.6), maa://36663 (81.82), ***maa://22815 (23.08)</t>
         </is>
       </c>
       <c r="Y24" s="1" t="n"/>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="AF24" s="2" t="inlineStr">
         <is>
-          <t>maa://22523 (85.42), maa://36672 (80.39), maa://29910 (92.31), **maa://21440 (34.55)</t>
+          <t>maa://22523 (85.42), maa://36672 (80.77), maa://29910 (92.31), **maa://21440 (34.55)</t>
         </is>
       </c>
       <c r="AG24" s="1" t="n"/>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>maa://41802 (100.0)</t>
+          <t>maa://41802 (91.67)</t>
         </is>
       </c>
       <c r="E26" s="1" t="n"/>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>maa://24913 (91.36)</t>
+          <t>maa://24913 (91.46)</t>
         </is>
       </c>
       <c r="I26" s="1" t="n"/>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>maa://42235 (92.86)</t>
+          <t>maa://42235 (92.96)</t>
         </is>
       </c>
       <c r="AC26" s="1" t="n"/>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="AF26" s="2" t="inlineStr">
         <is>
-          <t>maa://30511 (83.33), *maa://29760 (64.29)</t>
+          <t>maa://30511 (83.78), *maa://29760 (64.29)</t>
         </is>
       </c>
       <c r="AG26" s="1" t="n"/>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>*maa://30624 (76.0)</t>
+          <t>*maa://30624 (76.47)</t>
         </is>
       </c>
       <c r="U27" s="1" t="n"/>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="AF27" s="2" t="inlineStr">
         <is>
-          <t>maa://24023 (97.01)</t>
+          <t>maa://24023 (97.06)</t>
         </is>
       </c>
       <c r="AG27" s="1" t="n"/>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>maa://24465 (90.72), maa://25725 (83.53)</t>
+          <t>maa://24465 (90.73), maa://25725 (83.53)</t>
         </is>
       </c>
       <c r="E28" s="1" t="n"/>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>maa://23263 (94.85), *maa://29765 (61.33)</t>
+          <t>maa://23263 (94.85), *maa://29765 (60.53)</t>
         </is>
       </c>
       <c r="U28" s="1" t="n"/>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>maa://39929 (89.4), ***maa://39723 (14.29), maa://41749 (90.0)</t>
+          <t>maa://39929 (89.44), ***maa://39723 (14.29), maa://41749 (90.0)</t>
         </is>
       </c>
       <c r="Y28" s="1" t="n"/>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>maa://28432 (93.09), *maa://28440 (76.6), maa://31400 (100.0), *maa://28650 (71.43)</t>
+          <t>maa://28432 (93.11), *maa://28440 (76.6), maa://31400 (100.0), *maa://28650 (71.43)</t>
         </is>
       </c>
       <c r="M29" s="1" t="n"/>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>maa://42979 (97.94)</t>
+          <t>maa://42979 (97.96)</t>
         </is>
       </c>
       <c r="AC30" s="1" t="n"/>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>maa://35926 (93.89), maa://36258 (82.42), maa://43904 (100.0)</t>
+          <t>maa://35926 (93.92), maa://36258 (82.61), *maa://43904 (80.0)</t>
         </is>
       </c>
       <c r="M31" s="1" t="n"/>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>maa://41296 (96.3)</t>
+          <t>maa://41296 (96.33)</t>
         </is>
       </c>
       <c r="M35" s="1" t="n"/>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="AF38" s="2" t="inlineStr">
         <is>
-          <t>maa://36697 (86.21)</t>
+          <t>maa://36697 (85.71)</t>
         </is>
       </c>
       <c r="AG38" s="1" t="n"/>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>maa://24709 (91.87)</t>
+          <t>maa://24709 (91.94)</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n"/>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>maa://35931 (92.42), *maa://43901 (80.0)</t>
+          <t>maa://35931 (92.42), maa://43901 (83.33)</t>
         </is>
       </c>
       <c r="I46" s="1" t="n"/>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>*maa://37964 (55.56)</t>
+          <t>*maa://37964 (57.14)</t>
         </is>
       </c>
       <c r="I58" s="1" t="n"/>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>maa://44405 (100.0)</t>
+          <t>**maa://44405 (50.0)</t>
         </is>
       </c>
       <c r="I64" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单作者版.xlsx
+++ b/Excel/悖论模拟干员名单作者版.xlsx
@@ -750,7 +750,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>maa://21246 (91.41), maa://36684 (95.54), ***maa://22731 (6.25)</t>
+          <t>maa://21246 (91.41), maa://36684 (95.58), ***maa://22731 (6.25)</t>
         </is>
       </c>
       <c r="AC2" s="1" t="n"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>maa://25251 (91.53), ***maa://21730 (25.33), ***maa://39501 (16.13), **maa://36675 (50.0)</t>
+          <t>maa://25251 (91.53), ***maa://21730 (26.32), ***maa://39501 (15.62), **maa://36675 (50.0)</t>
         </is>
       </c>
       <c r="AG2" s="1" t="n"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>maa://36987 (96.08), maa://40192 (98.11), maa://39849 (88.89)</t>
+          <t>maa://36987 (96.08), maa://40192 (98.15), maa://39849 (88.89)</t>
         </is>
       </c>
       <c r="E3" s="1" t="n"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>maa://21247 (98.57), *maa://22748 (60.0)</t>
+          <t>maa://21247 (98.58), *maa://22748 (60.0)</t>
         </is>
       </c>
       <c r="I3" s="1" t="n"/>
@@ -914,7 +914,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>maa://24632 (94.12), **maa://24303 (33.33), maa://22499 (86.67), maa://22746 (100.0)</t>
+          <t>maa://24632 (94.15), **maa://24303 (33.33), maa://22499 (86.67), maa://22746 (100.0)</t>
         </is>
       </c>
       <c r="E4" s="1" t="n"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>maa://32509 (96.58), maa://27295 (85.92), maa://22754 (90.41), *maa://21746 (55.81), *maa://31008 (78.57)</t>
+          <t>maa://32509 (95.76), maa://27295 (85.92), maa://22754 (90.41), *maa://21746 (55.81), *maa://31008 (78.57)</t>
         </is>
       </c>
       <c r="U4" s="1" t="n"/>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>maa://28624 (92.73), maa://24957 (97.73)</t>
+          <t>maa://28624 (92.79), maa://24957 (97.73)</t>
         </is>
       </c>
       <c r="M7" s="1" t="n"/>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>maa://22399 (95.45), *maa://22758 (74.29)</t>
+          <t>maa://22399 (95.48), *maa://22758 (74.29)</t>
         </is>
       </c>
       <c r="Y7" s="1" t="n"/>
@@ -1429,7 +1429,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.02.22 13:17:25</t>
+          <t>更新日期：2025.02.26 13:18:30</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>maa://32931 (83.76), *maa://21916 (62.12), maa://23252 (91.18), maa://37496 (96.77), **maa://22759 (45.45)</t>
+          <t>maa://32931 (83.9), *maa://21916 (62.12), maa://23252 (91.18), maa://37496 (96.88), **maa://22759 (45.45)</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>maa://22765 (91.67), *maa://21915 (67.86)</t>
+          <t>maa://22765 (91.67), *maa://21915 (68.97)</t>
         </is>
       </c>
       <c r="E9" s="1" t="n"/>
@@ -1588,11 +1588,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="1" t="n"/>
       <c r="J9" s="1" t="inlineStr">
         <is>
@@ -1670,7 +1666,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>maa://28711 (86.89), ***maa://22740 (5.66), **maa://39938 (46.67), **maa://27377 (42.86), ***maa://25174 (19.05), maa://40166 (96.15), *maa://45044 (66.67)</t>
+          <t>maa://28711 (86.99), ***maa://22740 (5.66), **maa://39938 (46.67), **maa://27377 (42.86), ***maa://25174 (19.05), maa://40166 (96.3), *maa://45044 (66.67)</t>
         </is>
       </c>
       <c r="AC9" s="1" t="n"/>
@@ -1704,7 +1700,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>***maa://25695 (18.72), ***maa://39951 (15.69), ***maa://34206 (20.0), ***maa://39243 (25.0), *maa://45271 (57.58)</t>
+          <t>***maa://25695 (18.62), ***maa://39951 (14.81), ***maa://34206 (20.0), ***maa://39243 (25.0), *maa://45271 (58.33)</t>
         </is>
       </c>
       <c r="E10" s="1" t="n"/>
@@ -1816,7 +1812,7 @@
       </c>
       <c r="AF10" s="2" t="inlineStr">
         <is>
-          <t>*maa://25021 (54.26), *maa://22733 (60.0), **maa://22761 (50.0)</t>
+          <t>*maa://25021 (54.26), *maa://22733 (61.11), **maa://22761 (50.0)</t>
         </is>
       </c>
       <c r="AG10" s="1" t="n"/>
@@ -1898,7 +1894,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>maa://22747 (92.5), maa://22501 (97.7), maa://45521 (83.33)</t>
+          <t>maa://22747 (92.5), maa://22501 (97.73), maa://45521 (83.33)</t>
         </is>
       </c>
       <c r="U11" s="1" t="n"/>
@@ -1930,7 +1926,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>maa://29912 (97.14), maa://22516 (88.37), *maa://20794 (52.24)</t>
+          <t>maa://29912 (97.18), maa://22516 (88.37), *maa://20794 (52.24)</t>
         </is>
       </c>
       <c r="AC11" s="1" t="n"/>
@@ -2094,7 +2090,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>maa://24999 (92.1), maa://36673 (93.24), maa://25001 (85.71)</t>
+          <t>maa://24999 (92.11), maa://36673 (93.24), maa://25001 (85.71)</t>
         </is>
       </c>
       <c r="E13" s="1" t="n"/>
@@ -2142,7 +2138,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>maa://22676 (92.74), *maa://22583 (74.63), *maa://22500 (58.7)</t>
+          <t>maa://22676 (92.74), *maa://22583 (75.0), *maa://22500 (58.7)</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n"/>
@@ -2206,7 +2202,7 @@
       </c>
       <c r="AF13" s="2" t="inlineStr">
         <is>
-          <t>**maa://22737 (34.25), maa://39883 (91.43), *maa://39885 (53.33)</t>
+          <t>**maa://22737 (34.25), maa://39883 (91.67), *maa://39885 (53.33)</t>
         </is>
       </c>
       <c r="AG13" s="1" t="n"/>
@@ -2256,7 +2252,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>maa://26245 (96.71), maa://21288 (96.3), maa://39841 (95.24), maa://36682 (97.44)</t>
+          <t>maa://26245 (96.73), maa://21288 (96.3), maa://39841 (95.28), maa://36682 (97.44)</t>
         </is>
       </c>
       <c r="M14" s="1" t="n"/>
@@ -2288,7 +2284,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>maa://22521 (94.29), maa://42751 (100.0)</t>
+          <t>maa://22521 (94.34), maa://42751 (100.0)</t>
         </is>
       </c>
       <c r="U14" s="1" t="n"/>
@@ -2354,7 +2350,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>*maa://22743 (77.93), maa://22734 (84.17), *maa://30808 (64.18), **maa://36048 (45.0), maa://45058 (92.86)</t>
+          <t>*maa://22743 (78.04), maa://22734 (84.17), *maa://30808 (64.18), **maa://36048 (45.0), maa://45058 (92.86)</t>
         </is>
       </c>
       <c r="E15" s="1" t="n"/>
@@ -2434,7 +2430,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>maa://38786 (85.71)</t>
+          <t>*maa://38786 (75.0)</t>
         </is>
       </c>
       <c r="Y15" s="1" t="n"/>
@@ -2466,7 +2462,7 @@
       </c>
       <c r="AF15" s="2" t="inlineStr">
         <is>
-          <t>maa://21364 (81.02), *maa://36666 (78.5), *maa://22766 (68.64)</t>
+          <t>maa://21364 (81.02), *maa://36666 (78.9), *maa://22766 (68.64)</t>
         </is>
       </c>
       <c r="AG15" s="1" t="n"/>
@@ -2484,7 +2480,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>maa://21441 (96.4), maa://36679 (94.34), maa://37650 (97.14)</t>
+          <t>maa://21441 (96.4), maa://36679 (94.34), maa://37650 (97.3)</t>
         </is>
       </c>
       <c r="E16" s="1" t="n"/>
@@ -2548,7 +2544,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>maa://22729 (95.0), *maa://28648 (69.12), maa://36674 (82.69)</t>
+          <t>maa://22729 (95.03), *maa://28648 (69.12), maa://36674 (82.69)</t>
         </is>
       </c>
       <c r="U16" s="1" t="n"/>
@@ -2630,7 +2626,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>maa://22430 (88.72), maa://39599 (86.27)</t>
+          <t>maa://22430 (88.78), maa://39599 (86.27)</t>
         </is>
       </c>
       <c r="I17" s="1" t="n"/>
@@ -2678,7 +2674,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>**maa://42324 (48.28)</t>
+          <t>**maa://42324 (50.0)</t>
         </is>
       </c>
       <c r="U17" s="1" t="n"/>
@@ -2744,7 +2740,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>maa://24570 (97.33)</t>
+          <t>maa://24570 (97.35)</t>
         </is>
       </c>
       <c r="E18" s="1" t="n"/>
@@ -2776,7 +2772,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>maa://22466 (90.3), *maa://22732 (51.11)</t>
+          <t>maa://22466 (90.36), *maa://22732 (50.55)</t>
         </is>
       </c>
       <c r="M18" s="1" t="n"/>
@@ -2970,7 +2966,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>*maa://30709 (65.75), *maa://36668 (57.5)</t>
+          <t>*maa://30709 (65.83), *maa://36668 (57.5)</t>
         </is>
       </c>
       <c r="AC19" s="1" t="n"/>
@@ -3004,7 +3000,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>maa://21432 (90.12), maa://25198 (93.64), *maa://20795 (50.77), maa://36680 (91.18)</t>
+          <t>maa://21432 (90.17), maa://25198 (93.64), *maa://20795 (50.77), maa://36680 (91.18)</t>
         </is>
       </c>
       <c r="E20" s="1" t="n"/>
@@ -3036,7 +3032,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>maa://41331 (84.97)</t>
+          <t>maa://41331 (85.06)</t>
         </is>
       </c>
       <c r="M20" s="1" t="n"/>
@@ -3134,7 +3130,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>maa://21261 (97.56)</t>
+          <t>maa://21261 (97.62)</t>
         </is>
       </c>
       <c r="E21" s="1" t="n"/>
@@ -3150,7 +3146,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>maa://24372 (96.97)</t>
+          <t>maa://24372 (97.0)</t>
         </is>
       </c>
       <c r="I21" s="1" t="n"/>
@@ -3182,7 +3178,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>maa://24381 (84.21)</t>
+          <t>maa://24381 (85.0)</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n"/>
@@ -3230,7 +3226,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>maa://21443 (81.07), ***maa://23820 (30.0)</t>
+          <t>maa://21443 (81.12), ***maa://23820 (30.0)</t>
         </is>
       </c>
       <c r="AC21" s="1" t="n"/>
@@ -3296,7 +3292,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>maa://27127 (80.17), *maa://22751 (71.01)</t>
+          <t>*maa://27127 (79.66), *maa://22751 (71.01)</t>
         </is>
       </c>
       <c r="M22" s="1" t="n"/>
@@ -3426,7 +3422,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>maa://39756 (95.64), maa://39875 (94.44)</t>
+          <t>maa://39756 (95.68), maa://39875 (94.44)</t>
         </is>
       </c>
       <c r="M23" s="1" t="n"/>
@@ -3474,7 +3470,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>*maa://28503 (68.35)</t>
+          <t>*maa://28503 (68.75)</t>
         </is>
       </c>
       <c r="Y23" s="1" t="n"/>
@@ -3524,7 +3520,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>*maa://24368 (78.16), **maa://46650 (50.0)</t>
+          <t>*maa://24368 (78.16), *maa://46650 (60.0)</t>
         </is>
       </c>
       <c r="E24" s="1" t="n"/>
@@ -3604,7 +3600,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>maa://29988 (84.65), maa://23504 (93.14), **maa://22892 (40.14), *maa://25141 (77.1), *maa://36663 (77.92), ***maa://22815 (23.08)</t>
+          <t>maa://29988 (84.65), maa://23504 (93.16), **maa://22892 (40.14), *maa://25141 (77.1), *maa://36663 (78.21), ***maa://22815 (23.08)</t>
         </is>
       </c>
       <c r="Y24" s="1" t="n"/>
@@ -3636,7 +3632,7 @@
       </c>
       <c r="AF24" s="2" t="inlineStr">
         <is>
-          <t>maa://22523 (86.0), maa://36672 (80.36), maa://29910 (93.1), **maa://21440 (35.71), *maa://45831 (75.0)</t>
+          <t>maa://22523 (86.0), maa://36672 (80.36), maa://29910 (93.22), **maa://21440 (35.71), *maa://45831 (75.0)</t>
         </is>
       </c>
       <c r="AG24" s="1" t="n"/>
@@ -3654,7 +3650,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>maa://29753 (95.15)</t>
+          <t>maa://29753 (95.17)</t>
         </is>
       </c>
       <c r="E25" s="1" t="n"/>
@@ -3718,7 +3714,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>maa://20109 (92.09), maa://22545 (100.0), *maa://42915 (75.0)</t>
+          <t>maa://20109 (92.13), maa://22545 (100.0), *maa://42915 (75.0)</t>
         </is>
       </c>
       <c r="U25" s="1" t="n"/>
@@ -3750,7 +3746,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>maa://31215 (87.83), maa://24516 (80.22), maa://26001 (87.5)</t>
+          <t>maa://31215 (87.93), maa://24516 (80.22), maa://26001 (87.5)</t>
         </is>
       </c>
       <c r="AC25" s="1" t="n"/>
@@ -3784,7 +3780,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>maa://41802 (93.75)</t>
+          <t>maa://41802 (94.12)</t>
         </is>
       </c>
       <c r="E26" s="1" t="n"/>
@@ -3880,7 +3876,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>maa://42235 (94.06)</t>
+          <t>maa://42235 (94.12)</t>
         </is>
       </c>
       <c r="AC26" s="1" t="n"/>
@@ -3896,7 +3892,7 @@
       </c>
       <c r="AF26" s="2" t="inlineStr">
         <is>
-          <t>maa://30511 (82.5), *maa://29760 (60.0)</t>
+          <t>maa://30511 (80.49), *maa://29760 (60.0)</t>
         </is>
       </c>
       <c r="AG26" s="1" t="n"/>
@@ -4044,7 +4040,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>maa://24465 (91.04), maa://25725 (83.72)</t>
+          <t>maa://24465 (90.93), maa://25725 (83.91)</t>
         </is>
       </c>
       <c r="E28" s="1" t="n"/>
@@ -4108,7 +4104,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>*maa://29765 (63.41), maa://23263 (95.28)</t>
+          <t>*maa://29765 (63.86), maa://23263 (95.28)</t>
         </is>
       </c>
       <c r="U28" s="1" t="n"/>
@@ -4124,7 +4120,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>maa://39929 (90.65), maa://41749 (90.7), ***maa://39723 (13.89)</t>
+          <t>maa://39929 (90.7), maa://41749 (90.7), ***maa://39723 (13.89)</t>
         </is>
       </c>
       <c r="Y28" s="1" t="n"/>
@@ -4156,7 +4152,7 @@
       </c>
       <c r="AF28" s="2" t="inlineStr">
         <is>
-          <t>maa://36660 (92.2), *maa://36701 (66.67)</t>
+          <t>maa://36660 (92.24), *maa://36701 (66.67)</t>
         </is>
       </c>
       <c r="AG28" s="1" t="n"/>
@@ -4206,7 +4202,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>maa://28432 (93.45), *maa://28440 (79.82), maa://31400 (98.81), *maa://28650 (71.43)</t>
+          <t>maa://28432 (93.45), *maa://28440 (80.0), maa://31400 (98.81), *maa://28650 (71.43)</t>
         </is>
       </c>
       <c r="M29" s="1" t="n"/>
@@ -4286,7 +4282,7 @@
       </c>
       <c r="AF29" s="2" t="inlineStr">
         <is>
-          <t>*maa://24080 (68.85), maa://42865 (80.65), ***maa://34960 (8.33)</t>
+          <t>*maa://24080 (68.85), maa://42865 (80.95), ***maa://34960 (8.33)</t>
         </is>
       </c>
       <c r="AG29" s="1" t="n"/>
@@ -4400,7 +4396,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>maa://42979 (96.91), maa://45822 (100.0), *maa://45045 (80.0)</t>
+          <t>maa://42979 (96.97), maa://45822 (100.0), *maa://45045 (80.0)</t>
         </is>
       </c>
       <c r="AC30" s="1" t="n"/>
@@ -4466,7 +4462,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>maa://35926 (93.47), maa://36258 (85.34), *maa://43904 (72.73)</t>
+          <t>maa://35926 (93.47), maa://36258 (85.47), *maa://43904 (72.73)</t>
         </is>
       </c>
       <c r="M31" s="1" t="n"/>
@@ -4580,7 +4576,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>maa://21895 (97.5), maa://36667 (97.62), **maa://20793 (38.78), maa://22760 (100.0)</t>
+          <t>maa://21895 (97.01), maa://36667 (97.62), **maa://20793 (38.78), maa://22760 (100.0)</t>
         </is>
       </c>
       <c r="I32" s="1" t="n"/>
@@ -4628,7 +4624,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>maa://42859 (95.83), maa://41108 (88.0), maa://41238 (97.12), maa://45523 (100.0)</t>
+          <t>maa://42859 (95.93), maa://41108 (88.0), maa://41238 (97.12), maa://45523 (100.0)</t>
         </is>
       </c>
       <c r="U32" s="1" t="n"/>
@@ -4936,7 +4932,7 @@
       </c>
       <c r="AF34" s="2" t="inlineStr">
         <is>
-          <t>*maa://32650 (68.75)</t>
+          <t>*maa://32650 (70.59)</t>
         </is>
       </c>
       <c r="AG34" s="1" t="n"/>
@@ -5198,7 +5194,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>maa://45718 (98.5), *maa://47069 (75.0), maa://45789 (100.0)</t>
+          <t>maa://45718 (98.55), *maa://47069 (69.23), maa://45789 (100.0)</t>
         </is>
       </c>
       <c r="M37" s="1" t="n"/>
@@ -5214,7 +5210,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>maa://21280 (89.35), *maa://21239 (66.67)</t>
+          <t>maa://21280 (89.4), *maa://21239 (66.67)</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n"/>
@@ -5363,7 +5359,7 @@
       </c>
       <c r="AF38" s="2" t="inlineStr">
         <is>
-          <t>maa://36697 (86.32)</t>
+          <t>maa://36697 (86.38)</t>
         </is>
       </c>
       <c r="AG38" s="1" t="n"/>
@@ -5384,7 +5380,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>maa://36670 (89.11), maa://25199 (84.82), maa://30434 (91.36), ***maa://25036 (16.0), maa://45059 (81.25), *maa://44165 (66.67)</t>
+          <t>maa://36670 (89.11), maa://25199 (84.82), maa://30434 (91.46), ***maa://25036 (16.0), maa://45059 (81.25), *maa://44165 (66.67)</t>
         </is>
       </c>
       <c r="I39" s="1" t="n"/>
@@ -5432,7 +5428,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>maa://45788 (81.25), *maa://45790 (75.0), maa://47079 (92.31)</t>
+          <t>maa://45788 (81.25), *maa://45790 (75.0), maa://47079 (93.75)</t>
         </is>
       </c>
       <c r="U39" s="1" t="n"/>
@@ -5846,7 +5842,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>maa://21229 (84.74), maa://30807 (95.65), *maa://22767 (55.0), ***maa://20796 (13.79), maa://42459 (84.21)</t>
+          <t>maa://21229 (84.82), maa://30807 (95.65), *maa://22767 (55.0), ***maa://20796 (13.79), maa://42459 (85.0)</t>
         </is>
       </c>
       <c r="I45" s="1" t="n"/>
@@ -5899,7 +5895,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>maa://35931 (91.93), maa://43901 (92.31)</t>
+          <t>maa://35931 (91.95), maa://43901 (92.59)</t>
         </is>
       </c>
       <c r="I46" s="1" t="n"/>
@@ -6245,7 +6241,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>maa://32534 (94.07), **maa://32434 (33.33)</t>
+          <t>maa://32534 (94.08), **maa://32434 (33.33)</t>
         </is>
       </c>
       <c r="I53" s="1" t="n"/>
@@ -6281,7 +6277,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>maa://32532 (92.16)</t>
+          <t>maa://32532 (92.21)</t>
         </is>
       </c>
       <c r="I55" s="1" t="n"/>
@@ -6335,7 +6331,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>*maa://37964 (62.16)</t>
+          <t>*maa://37964 (60.53)</t>
         </is>
       </c>
       <c r="I58" s="1" t="n"/>
@@ -6353,7 +6349,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>maa://31270 (95.31), maa://27746 (82.3)</t>
+          <t>maa://31270 (95.35), maa://27746 (82.3)</t>
         </is>
       </c>
       <c r="I59" s="1" t="n"/>
@@ -6371,7 +6367,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>*maa://40438 (68.33)</t>
+          <t>*maa://40438 (68.85)</t>
         </is>
       </c>
       <c r="I60" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单作者版.xlsx
+++ b/Excel/悖论模拟干员名单作者版.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>maa://24702 (94.5), maa://25390 (96.2), maa://36681 (87.34)</t>
+          <t>maa://24702 (94.52), maa://25390 (96.2), maa://36681 (87.34)</t>
         </is>
       </c>
       <c r="E2" s="1" t="n"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>maa://21247 (98.58), *maa://22748 (60.0)</t>
+          <t>maa://21247 (98.59), *maa://22748 (60.0)</t>
         </is>
       </c>
       <c r="I3" s="1" t="n"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>*maa://22880 (65.15), maa://20276 (86.52), *maa://22749 (72.73)</t>
+          <t>*maa://22880 (65.33), maa://20276 (86.52), *maa://22749 (72.73)</t>
         </is>
       </c>
       <c r="M3" s="1" t="n"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>maa://24617 (89.74), **maa://20790 (43.48), ***maa://37170 (16.67), maa://45854 (86.36)</t>
+          <t>maa://24617 (89.74), **maa://20790 (43.48), ***maa://37170 (16.67), maa://45854 (86.96)</t>
         </is>
       </c>
       <c r="U3" s="1" t="n"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>maa://27396 (84.31), maa://27484 (96.55), maa://27480 (83.33)</t>
+          <t>maa://27396 (84.36), maa://27484 (96.55), maa://27480 (83.33)</t>
         </is>
       </c>
       <c r="Y3" s="1" t="n"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>**maa://32495 (48.7), ***maa://31785 (22.22), maa://43217 (90.48), ***maa://36683 (28.26)</t>
+          <t>**maa://32495 (48.7), ***maa://31785 (22.22), maa://43217 (90.62), ***maa://36683 (28.26)</t>
         </is>
       </c>
       <c r="Y4" s="1" t="n"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>*maa://22757 (78.38)</t>
+          <t>*maa://22757 (76.32)</t>
         </is>
       </c>
       <c r="M5" s="1" t="n"/>
@@ -1429,7 +1429,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.02 13:19:18</t>
+          <t>更新日期：2025.03.03 13:19:02</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>maa://28711 (86.99), ***maa://22740 (5.66), **maa://39938 (46.67), **maa://27377 (42.86), ***maa://25174 (19.05), maa://40166 (96.3), *maa://45044 (66.67)</t>
+          <t>maa://28711 (87.1), ***maa://22740 (5.66), **maa://39938 (46.67), **maa://27377 (42.86), ***maa://25174 (19.05), maa://40166 (96.3), *maa://45044 (66.67)</t>
         </is>
       </c>
       <c r="AC9" s="1" t="n"/>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>***maa://25695 (18.62), ***maa://39951 (14.81), ***maa://34206 (20.0), ***maa://39243 (25.0), *maa://45271 (57.89)</t>
+          <t>***maa://25695 (18.62), ***maa://39951 (14.55), ***maa://34206 (20.0), ***maa://39243 (25.0), *maa://45271 (57.89)</t>
         </is>
       </c>
       <c r="E10" s="1" t="n"/>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>maa://27395 (96.48), maa://22755 (87.83), **maa://22756 (40.91), ***maa://21737 (10.61)</t>
+          <t>maa://27395 (96.5), maa://22755 (87.83), **maa://22756 (40.91), ***maa://21737 (10.61)</t>
         </is>
       </c>
       <c r="U10" s="1" t="n"/>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>maa://22747 (92.5), maa://22501 (97.73), maa://45521 (84.21)</t>
+          <t>maa://22747 (92.5), maa://22501 (97.78), maa://45521 (85.0)</t>
         </is>
       </c>
       <c r="U11" s="1" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>maa://22753 (91.01), *maa://21485 (75.89), maa://37962 (90.24)</t>
+          <t>maa://22753 (91.06), *maa://21485 (75.89), maa://37962 (90.24)</t>
         </is>
       </c>
       <c r="Y12" s="1" t="n"/>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>maa://24999 (92.13), maa://36673 (93.33), maa://25001 (85.71)</t>
+          <t>maa://24999 (92.14), maa://36673 (93.33), maa://25001 (85.71)</t>
         </is>
       </c>
       <c r="E13" s="1" t="n"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>*maa://21248 (73.53), **maa://22728 (46.67)</t>
+          <t>*maa://21248 (73.22), **maa://22728 (46.67)</t>
         </is>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>maa://26245 (96.75), maa://21288 (96.3), maa://39841 (95.33), maa://36682 (97.44)</t>
+          <t>maa://26245 (96.75), maa://21288 (96.3), maa://39841 (95.37), maa://36682 (97.44)</t>
         </is>
       </c>
       <c r="M14" s="1" t="n"/>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>*maa://22743 (78.04), maa://22734 (84.17), *maa://30808 (64.18), **maa://36048 (45.0), maa://45058 (92.86)</t>
+          <t>*maa://22743 (78.04), maa://22734 (84.17), *maa://30808 (64.18), **maa://36048 (46.77), maa://45058 (92.86)</t>
         </is>
       </c>
       <c r="E15" s="1" t="n"/>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>maa://22430 (88.78), maa://39599 (86.27)</t>
+          <t>maa://22430 (88.83), maa://39599 (86.27)</t>
         </is>
       </c>
       <c r="I17" s="1" t="n"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>maa://24421 (88.98)</t>
+          <t>maa://24421 (89.02)</t>
         </is>
       </c>
       <c r="I18" s="1" t="n"/>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>maa://22466 (90.42), *maa://22732 (50.55)</t>
+          <t>maa://22466 (90.48), *maa://22732 (50.55)</t>
         </is>
       </c>
       <c r="M18" s="1" t="n"/>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>maa://21432 (90.17), maa://25198 (93.64), *maa://20795 (50.77), maa://36680 (91.18)</t>
+          <t>maa://21432 (90.23), maa://25198 (93.64), *maa://20795 (50.77), maa://36680 (91.18)</t>
         </is>
       </c>
       <c r="E20" s="1" t="n"/>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>maa://22864 (89.87)</t>
+          <t>maa://22864 (89.94)</t>
         </is>
       </c>
       <c r="I20" s="1" t="n"/>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AF21" s="2" t="inlineStr">
         <is>
-          <t>maa://22524 (94.17), *maa://22432 (77.03)</t>
+          <t>maa://22524 (94.17), *maa://22432 (77.33)</t>
         </is>
       </c>
       <c r="AG21" s="1" t="n"/>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>maa://25236 (95.6), **maa://21678 (48.94), **maa://22735 (42.86)</t>
+          <t>maa://25236 (95.65), **maa://21678 (48.94), **maa://22735 (42.86)</t>
         </is>
       </c>
       <c r="I22" s="1" t="n"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>maa://39756 (95.69), maa://39875 (94.44)</t>
+          <t>maa://39756 (95.71), maa://39875 (94.44)</t>
         </is>
       </c>
       <c r="M23" s="1" t="n"/>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>maa://30587 (91.92), *maa://29748 (75.97), ***maa://29785 (16.18), *maa://37566 (76.92)</t>
+          <t>maa://30587 (91.96), *maa://29748 (75.97), ***maa://29785 (16.18), *maa://37566 (76.92)</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>*maa://24368 (78.27), *maa://46650 (60.0)</t>
+          <t>*maa://24368 (78.27), **maa://46650 (50.0)</t>
         </is>
       </c>
       <c r="E24" s="1" t="n"/>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>maa://29988 (84.31), maa://23504 (93.19), **maa://22892 (40.14), *maa://25141 (77.1), *maa://36663 (76.92), ***maa://22815 (23.08)</t>
+          <t>maa://29988 (84.38), maa://23504 (93.19), **maa://22892 (40.14), *maa://25141 (77.1), *maa://36663 (76.92), ***maa://22815 (23.08)</t>
         </is>
       </c>
       <c r="Y24" s="1" t="n"/>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AF24" s="2" t="inlineStr">
         <is>
-          <t>maa://22523 (86.0), maa://36672 (80.36), maa://29910 (93.22), **maa://21440 (35.71), *maa://45831 (75.0)</t>
+          <t>maa://22523 (86.0), maa://36672 (80.36), maa://29910 (93.22), **maa://21440 (35.71), *maa://45831 (80.0)</t>
         </is>
       </c>
       <c r="AG24" s="1" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>maa://20109 (92.13), maa://22545 (100.0), *maa://42915 (75.0)</t>
+          <t>maa://20109 (92.18), maa://22545 (100.0), *maa://42915 (75.0)</t>
         </is>
       </c>
       <c r="U25" s="1" t="n"/>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AF25" s="2" t="inlineStr">
         <is>
-          <t>maa://20108 (96.35), maa://24621 (96.88), maa://36676 (97.06), maa://22771 (85.71), *maa://37772 (66.67)</t>
+          <t>maa://20108 (96.35), maa://24621 (96.9), maa://36676 (97.06), maa://22771 (85.71), *maa://37772 (66.67)</t>
         </is>
       </c>
       <c r="AG25" s="1" t="n"/>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>*maa://29765 (63.86), maa://23263 (95.28)</t>
+          <t>*maa://29765 (64.29), maa://23263 (95.28)</t>
         </is>
       </c>
       <c r="U28" s="1" t="n"/>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>maa://39929 (90.77), maa://41749 (90.7), ***maa://39723 (13.89)</t>
+          <t>maa://39929 (90.79), maa://41749 (90.8), ***maa://39723 (13.89)</t>
         </is>
       </c>
       <c r="Y28" s="1" t="n"/>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>maa://28432 (93.49), *maa://28440 (80.0), maa://31400 (98.81), *maa://28650 (71.43)</t>
+          <t>maa://28432 (93.53), maa://28440 (80.18), maa://31400 (98.81), *maa://28650 (71.43)</t>
         </is>
       </c>
       <c r="M29" s="1" t="n"/>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>maa://21895 (97.01), maa://36667 (97.62), **maa://20793 (38.78), maa://22760 (100.0)</t>
+          <t>maa://21895 (97.03), maa://36667 (97.62), **maa://20793 (38.78), maa://22760 (100.0)</t>
         </is>
       </c>
       <c r="I32" s="1" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>maa://42859 (95.97), maa://41108 (88.0), maa://41238 (97.12), maa://45523 (100.0)</t>
+          <t>maa://42859 (95.97), maa://41108 (88.0), maa://41238 (97.14), maa://45523 (100.0)</t>
         </is>
       </c>
       <c r="U32" s="1" t="n"/>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>maa://45718 (97.92), *maa://47069 (69.23), maa://45789 (100.0)</t>
+          <t>maa://45718 (97.93), *maa://47069 (69.23), maa://45789 (100.0)</t>
         </is>
       </c>
       <c r="M37" s="1" t="n"/>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>maa://21280 (89.4), *maa://21239 (66.67)</t>
+          <t>maa://21280 (89.45), *maa://21239 (66.67)</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n"/>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AF38" s="2" t="inlineStr">
         <is>
-          <t>maa://36697 (86.38)</t>
+          <t>maa://36697 (86.45)</t>
         </is>
       </c>
       <c r="AG38" s="1" t="n"/>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>maa://36670 (89.11), maa://25199 (84.82), maa://30434 (91.46), ***maa://25036 (16.0), maa://45059 (83.33), *maa://44165 (66.67)</t>
+          <t>maa://36670 (89.11), maa://25199 (84.82), maa://30434 (91.57), ***maa://25036 (16.0), maa://45059 (83.33), *maa://44165 (66.67)</t>
         </is>
       </c>
       <c r="I39" s="1" t="n"/>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>maa://45788 (81.63), maa://47079 (94.12), *maa://45790 (75.0)</t>
+          <t>maa://45788 (81.82), maa://47079 (94.12), *maa://45790 (75.0)</t>
         </is>
       </c>
       <c r="U39" s="1" t="n"/>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>maa://21229 (84.82), maa://30807 (95.65), *maa://22767 (55.0), ***maa://20796 (13.79), maa://42459 (85.71)</t>
+          <t>maa://21229 (84.82), maa://30807 (95.65), *maa://22767 (55.0), ***maa://20796 (13.79), maa://42459 (86.36)</t>
         </is>
       </c>
       <c r="I45" s="1" t="n"/>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>maa://32532 (91.91)</t>
+          <t>maa://32532 (91.94)</t>
         </is>
       </c>
       <c r="I55" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单作者版.xlsx
+++ b/Excel/悖论模拟干员名单作者版.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>maa://24702 (94.5), maa://25390 (96.2), maa://36681 (87.34)</t>
+          <t>maa://24702 (94.54), maa://25390 (96.2), maa://36681 (87.34)</t>
         </is>
       </c>
       <c r="E2" s="1" t="n"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>maa://40192 (98.15), maa://36987 (96.08), maa://39849 (88.89)</t>
+          <t>maa://40192 (98.18), maa://36987 (96.08), maa://39849 (88.89)</t>
         </is>
       </c>
       <c r="E3" s="1" t="n"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>maa://21247 (98.58), *maa://22748 (60.0)</t>
+          <t>maa://21247 (98.6), *maa://22748 (60.0)</t>
         </is>
       </c>
       <c r="I3" s="1" t="n"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>*maa://22880 (65.15), maa://20276 (86.52), *maa://22749 (72.73)</t>
+          <t>*maa://22880 (65.33), maa://20276 (86.59), *maa://22749 (75.0)</t>
         </is>
       </c>
       <c r="M3" s="1" t="n"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>maa://21249 (94.49), maa://26254 (96.55)</t>
+          <t>maa://21249 (94.54), maa://26254 (96.67)</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>maa://24617 (89.74), **maa://20790 (43.48), ***maa://37170 (16.67), maa://45854 (86.36)</t>
+          <t>maa://24617 (89.83), **maa://20790 (43.48), ***maa://37170 (16.67), maa://45854 (87.5)</t>
         </is>
       </c>
       <c r="U3" s="1" t="n"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>maa://27396 (84.31), maa://27484 (96.55), maa://27480 (83.33)</t>
+          <t>maa://27396 (84.36), maa://27484 (96.58), maa://27480 (83.33)</t>
         </is>
       </c>
       <c r="Y3" s="1" t="n"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>maa://32509 (95.76), maa://27295 (85.92), maa://22754 (90.41), *maa://21746 (55.81), *maa://31008 (78.57)</t>
+          <t>maa://32509 (95.76), maa://27295 (86.11), maa://22754 (90.41), *maa://21746 (55.81), *maa://31008 (78.57)</t>
         </is>
       </c>
       <c r="U4" s="1" t="n"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>**maa://32495 (48.7), ***maa://31785 (22.22), maa://43217 (90.48), ***maa://36683 (28.26)</t>
+          <t>**maa://32495 (48.7), ***maa://31785 (22.22), maa://43217 (90.62), ***maa://36683 (28.26)</t>
         </is>
       </c>
       <c r="Y4" s="1" t="n"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>maa://21245 (84.94), maa://22744 (84.0)</t>
+          <t>maa://21245 (84.58), maa://22744 (84.0)</t>
         </is>
       </c>
       <c r="E5" s="1" t="n"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>*maa://22757 (78.38)</t>
+          <t>*maa://22757 (76.32)</t>
         </is>
       </c>
       <c r="M5" s="1" t="n"/>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>maa://31836 (93.1), maa://30381 (92.86)</t>
+          <t>maa://31836 (93.1), maa://30381 (93.33)</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>maa://22750 (91.67)</t>
+          <t>maa://22750 (91.84)</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n"/>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>maa://22399 (95.48), *maa://22758 (74.29)</t>
+          <t>maa://22399 (95.51), *maa://22758 (74.29)</t>
         </is>
       </c>
       <c r="Y7" s="1" t="n"/>
@@ -1429,7 +1429,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.02 13:19:18</t>
+          <t>更新日期：2025.03.05 13:18:50</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>maa://32931 (83.9), *maa://21916 (62.12), maa://23252 (91.18), maa://37496 (96.97), **maa://22759 (45.45)</t>
+          <t>maa://32931 (84.03), *maa://21916 (62.12), maa://23252 (91.18), maa://37496 (96.97), **maa://22759 (45.45)</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n"/>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>maa://22736 (83.17)</t>
+          <t>maa://22736 (83.33)</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n"/>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>maa://26223 (97.92)</t>
+          <t>maa://26223 (97.93)</t>
         </is>
       </c>
       <c r="Y9" s="1" t="n"/>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>maa://28711 (86.99), ***maa://22740 (5.66), **maa://39938 (46.67), **maa://27377 (42.86), ***maa://25174 (19.05), maa://40166 (96.3), *maa://45044 (66.67)</t>
+          <t>maa://28711 (87.1), ***maa://22740 (5.66), **maa://39938 (46.67), **maa://27377 (42.86), ***maa://25174 (19.05), maa://40166 (96.3), *maa://45044 (66.67)</t>
         </is>
       </c>
       <c r="AC9" s="1" t="n"/>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="AF9" s="2" t="inlineStr">
         <is>
-          <t>maa://26206 (87.7), *maa://22865 (51.85)</t>
+          <t>maa://26206 (87.8), *maa://22865 (51.85)</t>
         </is>
       </c>
       <c r="AG9" s="1" t="n"/>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>***maa://25695 (18.62), ***maa://39951 (14.81), ***maa://34206 (20.0), ***maa://39243 (25.0), *maa://45271 (57.89)</t>
+          <t>***maa://25695 (18.62), ***maa://39951 (14.55), ***maa://34206 (19.23), ***maa://39243 (25.0), *maa://45271 (57.89)</t>
         </is>
       </c>
       <c r="E10" s="1" t="n"/>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>maa://28977 (89.41), maa://36669 (86.36), *maa://23264 (61.82)</t>
+          <t>maa://28977 (89.41), maa://36669 (86.67), *maa://23264 (61.82)</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n"/>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>maa://27395 (96.48), maa://22755 (87.83), **maa://22756 (40.91), ***maa://21737 (10.61)</t>
+          <t>maa://27395 (96.5), maa://22755 (87.83), **maa://22756 (40.91), ***maa://21737 (10.61)</t>
         </is>
       </c>
       <c r="U10" s="1" t="n"/>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>maa://21287 (89.32)</t>
+          <t>maa://21287 (89.42)</t>
         </is>
       </c>
       <c r="M11" s="1" t="n"/>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>maa://45557 (87.5)</t>
+          <t>maa://45557 (88.89)</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n"/>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>maa://22747 (92.5), maa://22501 (97.73), maa://45521 (84.21)</t>
+          <t>maa://22747 (92.5), maa://22501 (97.78), maa://45521 (85.0)</t>
         </is>
       </c>
       <c r="U11" s="1" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>maa://22753 (91.01), *maa://21485 (75.89), maa://37962 (90.24)</t>
+          <t>maa://22753 (91.06), *maa://21485 (75.35), maa://37962 (90.48)</t>
         </is>
       </c>
       <c r="Y12" s="1" t="n"/>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>maa://24999 (92.13), maa://36673 (93.33), maa://25001 (85.71)</t>
+          <t>maa://24999 (92.16), maa://36673 (93.33), maa://25001 (85.71)</t>
         </is>
       </c>
       <c r="E13" s="1" t="n"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>*maa://21248 (73.53), **maa://22728 (46.67)</t>
+          <t>*maa://21248 (73.33), **maa://22728 (46.67)</t>
         </is>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>maa://22676 (92.8), *maa://22583 (75.0), *maa://22500 (58.7)</t>
+          <t>maa://22676 (92.86), *maa://22583 (75.0), *maa://22500 (58.7)</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n"/>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>maa://26245 (96.75), maa://21288 (96.3), maa://39841 (95.33), maa://36682 (97.44)</t>
+          <t>maa://26245 (96.75), maa://21288 (96.3), maa://39841 (94.55), maa://36682 (97.44)</t>
         </is>
       </c>
       <c r="M14" s="1" t="n"/>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>*maa://22743 (78.04), maa://22734 (84.17), *maa://30808 (64.18), **maa://36048 (45.0), maa://45058 (92.86)</t>
+          <t>*maa://22743 (78.04), maa://22734 (84.17), *maa://30808 (64.18), **maa://36048 (46.77), maa://45058 (92.86)</t>
         </is>
       </c>
       <c r="E15" s="1" t="n"/>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>maa://24304 (88.07), maa://21478 (89.19)</t>
+          <t>maa://24304 (88.13), maa://21478 (89.19)</t>
         </is>
       </c>
       <c r="I15" s="1" t="n"/>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>*maa://38786 (75.0)</t>
+          <t>*maa://38786 (66.67)</t>
         </is>
       </c>
       <c r="Y15" s="1" t="n"/>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AF15" s="2" t="inlineStr">
         <is>
-          <t>maa://21364 (80.78), *maa://36666 (77.68), *maa://22766 (68.64)</t>
+          <t>maa://21364 (80.84), *maa://36666 (77.68), *maa://22766 (68.64)</t>
         </is>
       </c>
       <c r="AG15" s="1" t="n"/>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>maa://22430 (88.78), maa://39599 (86.27)</t>
+          <t>maa://22430 (88.83), maa://39599 (86.27)</t>
         </is>
       </c>
       <c r="I17" s="1" t="n"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>maa://24421 (88.98)</t>
+          <t>maa://24421 (89.02)</t>
         </is>
       </c>
       <c r="I18" s="1" t="n"/>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>maa://22466 (90.42), *maa://22732 (50.55)</t>
+          <t>maa://22466 (90.53), *maa://22732 (50.55)</t>
         </is>
       </c>
       <c r="M18" s="1" t="n"/>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>maa://21432 (90.17), maa://25198 (93.64), *maa://20795 (50.77), maa://36680 (91.18)</t>
+          <t>maa://21432 (90.23), maa://25198 (93.64), *maa://20795 (50.77), maa://36680 (91.18)</t>
         </is>
       </c>
       <c r="E20" s="1" t="n"/>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>maa://22864 (89.87)</t>
+          <t>maa://22864 (89.94)</t>
         </is>
       </c>
       <c r="I20" s="1" t="n"/>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>maa://41331 (85.16)</t>
+          <t>maa://41331 (85.26)</t>
         </is>
       </c>
       <c r="M20" s="1" t="n"/>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>maa://31731 (96.08)</t>
+          <t>maa://31731 (96.15)</t>
         </is>
       </c>
       <c r="M21" s="1" t="n"/>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AF21" s="2" t="inlineStr">
         <is>
-          <t>maa://22524 (94.17), *maa://22432 (77.03)</t>
+          <t>maa://22524 (94.17), *maa://22432 (77.63)</t>
         </is>
       </c>
       <c r="AG21" s="1" t="n"/>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>maa://25236 (95.6), **maa://21678 (48.94), **maa://22735 (42.86)</t>
+          <t>maa://25236 (95.7), **maa://21678 (48.94), **maa://22735 (42.86)</t>
         </is>
       </c>
       <c r="I22" s="1" t="n"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>maa://39756 (95.69), maa://39875 (94.44)</t>
+          <t>maa://39756 (95.73), maa://39875 (94.44)</t>
         </is>
       </c>
       <c r="M23" s="1" t="n"/>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>maa://30587 (91.92), *maa://29748 (75.97), ***maa://29785 (16.18), *maa://37566 (76.92)</t>
+          <t>maa://30587 (92.0), *maa://29748 (75.97), ***maa://29785 (16.18), *maa://37566 (76.92)</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>*maa://24368 (78.27), *maa://46650 (60.0)</t>
+          <t>*maa://24368 (78.27), **maa://46650 (50.0)</t>
         </is>
       </c>
       <c r="E24" s="1" t="n"/>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>maa://29988 (84.31), maa://23504 (93.19), **maa://22892 (40.14), *maa://25141 (77.1), *maa://36663 (76.92), ***maa://22815 (23.08)</t>
+          <t>maa://29988 (84.44), maa://23504 (93.21), **maa://22892 (40.14), *maa://25141 (77.1), *maa://36663 (76.92), ***maa://22815 (23.08)</t>
         </is>
       </c>
       <c r="Y24" s="1" t="n"/>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AF24" s="2" t="inlineStr">
         <is>
-          <t>maa://22523 (86.0), maa://36672 (80.36), maa://29910 (93.22), **maa://21440 (35.71), *maa://45831 (75.0)</t>
+          <t>maa://22523 (85.57), maa://36672 (80.36), maa://29910 (93.22), **maa://21440 (35.71), *maa://45831 (80.0)</t>
         </is>
       </c>
       <c r="AG24" s="1" t="n"/>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>*maa://29063 (73.17), *maa://25311 (74.04), ***maa://22725 (4.84), *maa://45047 (62.5)</t>
+          <t>*maa://29063 (73.17), *maa://25311 (74.29), ***maa://22725 (4.84), *maa://45047 (62.5)</t>
         </is>
       </c>
       <c r="I25" s="1" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>maa://20109 (92.13), maa://22545 (100.0), *maa://42915 (75.0)</t>
+          <t>maa://20109 (92.18), maa://22545 (100.0), *maa://42915 (75.0)</t>
         </is>
       </c>
       <c r="U25" s="1" t="n"/>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AF25" s="2" t="inlineStr">
         <is>
-          <t>maa://20108 (96.35), maa://24621 (96.88), maa://36676 (97.06), maa://22771 (85.71), *maa://37772 (66.67)</t>
+          <t>maa://20108 (96.35), maa://24621 (96.9), maa://36676 (97.06), maa://22771 (85.71), *maa://37772 (66.67)</t>
         </is>
       </c>
       <c r="AG25" s="1" t="n"/>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>maa://42235 (94.17)</t>
+          <t>maa://42235 (94.23)</t>
         </is>
       </c>
       <c r="AC26" s="1" t="n"/>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>*maa://29765 (63.86), maa://23263 (95.28)</t>
+          <t>*maa://29765 (64.29), maa://23263 (95.28)</t>
         </is>
       </c>
       <c r="U28" s="1" t="n"/>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>maa://39929 (90.77), maa://41749 (90.7), ***maa://39723 (13.89)</t>
+          <t>maa://39929 (90.84), maa://41749 (90.8), ***maa://39723 (13.89)</t>
         </is>
       </c>
       <c r="Y28" s="1" t="n"/>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AF28" s="2" t="inlineStr">
         <is>
-          <t>maa://36660 (92.31), *maa://36701 (66.67)</t>
+          <t>maa://36660 (92.33), *maa://36701 (66.67)</t>
         </is>
       </c>
       <c r="AG28" s="1" t="n"/>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>maa://28432 (93.49), *maa://28440 (80.0), maa://31400 (98.81), *maa://28650 (71.43)</t>
+          <t>maa://28432 (93.53), maa://28440 (80.18), maa://31400 (98.81), *maa://28650 (71.43)</t>
         </is>
       </c>
       <c r="M29" s="1" t="n"/>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>maa://21442 (99.11)</t>
+          <t>maa://21442 (99.12)</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n"/>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>maa://35926 (93.49), maa://36258 (85.47), *maa://43904 (72.73)</t>
+          <t>maa://35926 (93.52), maa://36258 (85.47), *maa://43904 (72.73)</t>
         </is>
       </c>
       <c r="M31" s="1" t="n"/>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>maa://21895 (97.01), maa://36667 (97.62), **maa://20793 (38.78), maa://22760 (100.0)</t>
+          <t>maa://21895 (97.03), maa://36667 (97.62), **maa://20793 (38.78), maa://22760 (100.0)</t>
         </is>
       </c>
       <c r="I32" s="1" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>maa://42859 (95.97), maa://41108 (88.0), maa://41238 (97.12), maa://45523 (100.0)</t>
+          <t>maa://42859 (95.97), maa://41108 (88.0), maa://41238 (97.14), maa://45523 (100.0)</t>
         </is>
       </c>
       <c r="U32" s="1" t="n"/>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>maa://21956 (81.08), *maa://22730 (79.31)</t>
+          <t>maa://21956 (81.21), *maa://22730 (79.31)</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>maa://24526 (93.08)</t>
+          <t>maa://24526 (93.1)</t>
         </is>
       </c>
       <c r="U34" s="1" t="n"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>maa://41296 (96.27)</t>
+          <t>maa://41296 (96.3)</t>
         </is>
       </c>
       <c r="M35" s="1" t="n"/>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AF35" s="2" t="inlineStr">
         <is>
-          <t>maa://39479 (94.12)</t>
+          <t>maa://39479 (88.89)</t>
         </is>
       </c>
       <c r="AG35" s="1" t="n"/>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>*maa://24374 (56.82)</t>
+          <t>*maa://24374 (55.56)</t>
         </is>
       </c>
       <c r="I37" s="1" t="n"/>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>maa://45718 (97.92), *maa://47069 (69.23), maa://45789 (100.0)</t>
+          <t>maa://45718 (97.96), *maa://47069 (69.23), maa://45789 (100.0)</t>
         </is>
       </c>
       <c r="M37" s="1" t="n"/>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>maa://21280 (89.4), *maa://21239 (66.67)</t>
+          <t>maa://21280 (89.45), *maa://21239 (66.67)</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n"/>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AF38" s="2" t="inlineStr">
         <is>
-          <t>maa://36697 (86.38)</t>
+          <t>maa://36697 (86.45)</t>
         </is>
       </c>
       <c r="AG38" s="1" t="n"/>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>maa://36670 (89.11), maa://25199 (84.82), maa://30434 (91.46), ***maa://25036 (16.0), maa://45059 (83.33), *maa://44165 (66.67)</t>
+          <t>maa://36670 (89.11), maa://25199 (84.82), maa://30434 (91.57), ***maa://25036 (16.0), maa://45059 (83.33), *maa://44165 (66.67)</t>
         </is>
       </c>
       <c r="I39" s="1" t="n"/>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>maa://45788 (81.63), maa://47079 (94.12), *maa://45790 (75.0)</t>
+          <t>maa://45788 (81.82), maa://47079 (94.12), *maa://45790 (75.0)</t>
         </is>
       </c>
       <c r="U39" s="1" t="n"/>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>**maa://35616 (40.0), maa://43177 (90.91)</t>
+          <t>**maa://35616 (40.0), maa://43177 (91.3)</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n"/>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>maa://22525 (92.36), maa://21284 (85.42)</t>
+          <t>maa://22525 (92.41), maa://21284 (85.42)</t>
         </is>
       </c>
       <c r="I43" s="1" t="n"/>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>maa://21229 (84.82), maa://30807 (95.65), *maa://22767 (55.0), ***maa://20796 (13.79), maa://42459 (85.71)</t>
+          <t>maa://21229 (84.82), maa://30807 (95.65), *maa://22767 (55.0), ***maa://20796 (13.79), maa://42459 (86.36)</t>
         </is>
       </c>
       <c r="I45" s="1" t="n"/>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>**maa://39364 (38.71)</t>
+          <t>**maa://39364 (37.5)</t>
         </is>
       </c>
       <c r="U45" s="1" t="n"/>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>maa://32532 (91.91)</t>
+          <t>maa://32532 (91.94)</t>
         </is>
       </c>
       <c r="I55" s="1" t="n"/>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>*maa://37964 (61.54)</t>
+          <t>*maa://37964 (60.98)</t>
         </is>
       </c>
       <c r="I58" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单作者版.xlsx
+++ b/Excel/悖论模拟干员名单作者版.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>*maa://24633 (56.17), *maa://30515 (69.9), *maa://34787 (73.68), maa://39402 (92.19), ***maa://20792 (11.93), ***maa://29083 (27.78)</t>
+          <t>*maa://24633 (56.17), *maa://30515 (69.9), *maa://34787 (72.73), maa://39402 (92.19), ***maa://20792 (11.93), ***maa://29083 (27.78)</t>
         </is>
       </c>
       <c r="M2" s="1" t="n"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>maa://21246 (91.41), maa://36684 (95.65), ***maa://22731 (6.25)</t>
+          <t>maa://21246 (91.41), maa://36684 (95.69), ***maa://22731 (6.25)</t>
         </is>
       </c>
       <c r="AC2" s="1" t="n"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>maa://40192 (98.18), maa://36987 (96.08), maa://39849 (88.89)</t>
+          <t>maa://40192 (96.49), maa://36987 (96.08), maa://39849 (88.89)</t>
         </is>
       </c>
       <c r="E3" s="1" t="n"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>maa://21245 (84.58), maa://22744 (84.0)</t>
+          <t>maa://21245 (84.65), maa://22744 (84.0)</t>
         </is>
       </c>
       <c r="E5" s="1" t="n"/>
@@ -1429,7 +1429,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.08 16:37:02</t>
+          <t>更新日期：2025.03.09 13:14:58</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>**maa://22866 (30.19), maa://26222 (98.08)</t>
+          <t>**maa://22866 (30.19), maa://26222 (98.11)</t>
         </is>
       </c>
       <c r="U9" s="1" t="n"/>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>maa://26223 (97.96)</t>
+          <t>maa://26223 (97.97)</t>
         </is>
       </c>
       <c r="Y9" s="1" t="n"/>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>maa://22301 (97.75), maa://45828 (92.86), maa://22726 (100.0)</t>
+          <t>maa://22301 (97.76), maa://45828 (92.86), maa://22726 (100.0)</t>
         </is>
       </c>
       <c r="Y10" s="1" t="n"/>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>maa://22747 (92.55), maa://22501 (97.78), maa://45521 (85.0)</t>
+          <t>maa://22747 (92.55), maa://22501 (97.78), maa://45521 (85.71)</t>
         </is>
       </c>
       <c r="U11" s="1" t="n"/>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>maa://26245 (96.75), maa://21288 (96.3), maa://39841 (94.55), maa://36682 (97.44)</t>
+          <t>maa://26245 (96.75), maa://21288 (96.3), maa://39841 (94.59), maa://36682 (97.44)</t>
         </is>
       </c>
       <c r="M14" s="1" t="n"/>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>maa://26228 (95.96)</t>
+          <t>maa://26228 (96.0)</t>
         </is>
       </c>
       <c r="AC16" s="1" t="n"/>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AF16" s="2" t="inlineStr">
         <is>
-          <t>*maa://23911 (65.09), maa://27755 (93.55)</t>
+          <t>*maa://23911 (65.09), maa://27755 (93.62)</t>
         </is>
       </c>
       <c r="AG16" s="1" t="n"/>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>**maa://42324 (50.0)</t>
+          <t>*maa://42324 (51.61)</t>
         </is>
       </c>
       <c r="U17" s="1" t="n"/>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>maa://24393 (97.92)</t>
+          <t>maa://24393 (97.96)</t>
         </is>
       </c>
       <c r="AC18" s="1" t="n"/>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>*maa://30709 (65.91), *maa://36668 (57.5)</t>
+          <t>*maa://30709 (65.99), *maa://36668 (57.5)</t>
         </is>
       </c>
       <c r="AC19" s="1" t="n"/>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>maa://21432 (90.34), maa://25198 (93.64), *maa://20795 (50.77), maa://36680 (91.18)</t>
+          <t>maa://21432 (90.34), maa://25198 (93.69), *maa://20795 (50.77), maa://36680 (91.18)</t>
         </is>
       </c>
       <c r="E20" s="1" t="n"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>maa://39756 (95.81), maa://39875 (94.52)</t>
+          <t>maa://39756 (95.83), maa://39875 (94.52)</t>
         </is>
       </c>
       <c r="M23" s="1" t="n"/>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>maa://29988 (84.11), maa://23504 (93.24), **maa://22892 (40.14), *maa://25141 (77.1), *maa://36663 (76.92), ***maa://22815 (23.08)</t>
+          <t>maa://29988 (84.11), maa://23504 (93.27), **maa://22892 (40.14), *maa://25141 (77.1), *maa://36663 (76.92), ***maa://22815 (23.08)</t>
         </is>
       </c>
       <c r="Y24" s="1" t="n"/>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>maa://24913 (92.22)</t>
+          <t>maa://24913 (91.21)</t>
         </is>
       </c>
       <c r="I26" s="1" t="n"/>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>maa://30770 (81.25)</t>
+          <t>maa://30770 (81.63)</t>
         </is>
       </c>
       <c r="M28" s="1" t="n"/>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>maa://39929 (90.68), maa://41749 (90.91), ***maa://39723 (13.89)</t>
+          <t>maa://39929 (90.68), maa://41749 (91.01), ***maa://39723 (13.89)</t>
         </is>
       </c>
       <c r="Y28" s="1" t="n"/>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>maa://28432 (93.55), maa://28440 (80.36), maa://31400 (98.82), *maa://28650 (71.43)</t>
+          <t>maa://28432 (93.55), maa://28440 (80.53), maa://31400 (98.82), *maa://28650 (71.43)</t>
         </is>
       </c>
       <c r="M29" s="1" t="n"/>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>maa://39477 (90.0)</t>
+          <t>maa://39477 (90.48)</t>
         </is>
       </c>
       <c r="Y30" s="1" t="n"/>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>maa://35926 (93.52), maa://36258 (84.75), *maa://43904 (72.73)</t>
+          <t>maa://35926 (93.52), maa://36258 (84.87), *maa://43904 (72.73)</t>
         </is>
       </c>
       <c r="M31" s="1" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>maa://42859 (96.0), maa://41108 (88.0), maa://41238 (97.14), maa://45523 (100.0)</t>
+          <t>maa://42859 (96.03), maa://41108 (88.0), maa://41238 (97.17), maa://45523 (100.0)</t>
         </is>
       </c>
       <c r="U32" s="1" t="n"/>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>maa://45718 (98.01), *maa://47069 (73.33), maa://45789 (100.0)</t>
+          <t>maa://45718 (98.04), *maa://47069 (73.33), maa://45789 (100.0)</t>
         </is>
       </c>
       <c r="M37" s="1" t="n"/>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>maa://21280 (89.5), *maa://21239 (66.67)</t>
+          <t>maa://21280 (89.55), *maa://21239 (66.67)</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n"/>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AF38" s="2" t="inlineStr">
         <is>
-          <t>maa://36697 (86.45)</t>
+          <t>maa://36697 (86.51)</t>
         </is>
       </c>
       <c r="AG38" s="1" t="n"/>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>maa://45788 (82.18), maa://47079 (94.12), *maa://45790 (76.92)</t>
+          <t>maa://45788 (82.35), maa://47079 (90.0), *maa://45790 (76.92)</t>
         </is>
       </c>
       <c r="U39" s="1" t="n"/>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>maa://35931 (91.95), maa://43901 (93.1)</t>
+          <t>maa://35931 (91.98), maa://43901 (93.1)</t>
         </is>
       </c>
       <c r="I46" s="1" t="n"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>maa://32534 (94.12), **maa://32434 (33.33)</t>
+          <t>maa://32534 (94.15), **maa://32434 (33.33)</t>
         </is>
       </c>
       <c r="I53" s="1" t="n"/>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>maa://32532 (91.96)</t>
+          <t>maa://32532 (91.99)</t>
         </is>
       </c>
       <c r="I55" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单作者版.xlsx
+++ b/Excel/悖论模拟干员名单作者版.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>*maa://24633 (56.17), *maa://30515 (69.9), *maa://34787 (73.68), maa://39402 (92.19), ***maa://20792 (11.93), ***maa://29083 (27.78)</t>
+          <t>*maa://24633 (56.17), *maa://30515 (69.9), *maa://34787 (72.73), maa://39402 (92.19), ***maa://20792 (11.93), ***maa://29083 (27.78)</t>
         </is>
       </c>
       <c r="M2" s="1" t="n"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>maa://21246 (91.41), maa://36684 (95.65), ***maa://22731 (6.25)</t>
+          <t>maa://21246 (91.41), maa://36684 (95.69), ***maa://22731 (6.25)</t>
         </is>
       </c>
       <c r="AC2" s="1" t="n"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>maa://40192 (98.18), maa://36987 (96.08), maa://39849 (88.89)</t>
+          <t>maa://40192 (96.49), maa://36987 (96.08), maa://39849 (88.89)</t>
         </is>
       </c>
       <c r="E3" s="1" t="n"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>**maa://32495 (48.7), ***maa://31785 (22.22), maa://43217 (90.91), ***maa://36683 (28.26)</t>
+          <t>**maa://32495 (48.7), ***maa://31785 (22.22), maa://43217 (91.18), ***maa://36683 (28.26)</t>
         </is>
       </c>
       <c r="Y4" s="1" t="n"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>maa://21245 (84.58), maa://22744 (84.0)</t>
+          <t>maa://21245 (84.65), maa://22744 (84.0)</t>
         </is>
       </c>
       <c r="E5" s="1" t="n"/>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>maa://42407 (96.49)</t>
+          <t>maa://42407 (96.55)</t>
         </is>
       </c>
       <c r="E6" s="1" t="n"/>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="AF6" s="2" t="inlineStr">
         <is>
-          <t>*maa://33152 (64.15), ***maa://22770 (26.09)</t>
+          <t>*maa://33152 (64.81), ***maa://22770 (26.09)</t>
         </is>
       </c>
       <c r="AG6" s="1" t="n"/>
@@ -1429,7 +1429,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.08 16:37:02</t>
+          <t>更新日期：2025.03.10 13:15:47</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>maa://21411 (95.96)</t>
+          <t>maa://21411 (95.97)</t>
         </is>
       </c>
       <c r="Y8" s="1" t="n"/>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>maa://22762 (92.31), *maa://39552 (80.0)</t>
+          <t>maa://22762 (92.39), *maa://39552 (80.0)</t>
         </is>
       </c>
       <c r="M9" s="1" t="n"/>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>**maa://22866 (30.19), maa://26222 (98.08)</t>
+          <t>**maa://22866 (30.19), maa://26222 (98.11)</t>
         </is>
       </c>
       <c r="U9" s="1" t="n"/>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>maa://26223 (97.96)</t>
+          <t>maa://26223 (97.97)</t>
         </is>
       </c>
       <c r="Y9" s="1" t="n"/>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>**maa://24395 (40.62)</t>
+          <t>**maa://24395 (39.39)</t>
         </is>
       </c>
       <c r="M10" s="1" t="n"/>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>maa://22301 (97.75), maa://45828 (92.86), maa://22726 (100.0)</t>
+          <t>maa://22301 (97.76), maa://45828 (92.86), maa://22726 (100.0)</t>
         </is>
       </c>
       <c r="Y10" s="1" t="n"/>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>maa://36707 (99.48)</t>
+          <t>maa://36707 (99.49)</t>
         </is>
       </c>
       <c r="E11" s="1" t="n"/>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>maa://22747 (92.55), maa://22501 (97.78), maa://45521 (85.0)</t>
+          <t>maa://22747 (92.55), maa://22501 (97.78), maa://45521 (85.71)</t>
         </is>
       </c>
       <c r="U11" s="1" t="n"/>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>maa://21867 (90.0), **maa://45826 (33.33)</t>
+          <t>maa://21867 (90.0), ***maa://45826 (28.57)</t>
         </is>
       </c>
       <c r="I12" s="1" t="n"/>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>maa://24999 (92.17), maa://36673 (93.33), maa://25001 (85.71)</t>
+          <t>maa://24999 (92.18), maa://36673 (92.11), maa://25001 (85.71)</t>
         </is>
       </c>
       <c r="E13" s="1" t="n"/>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>maa://22676 (92.97), *maa://22583 (75.0), *maa://22500 (58.7)</t>
+          <t>maa://22676 (93.02), *maa://22583 (75.0), *maa://22500 (58.7)</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n"/>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>maa://30764 (87.5)</t>
+          <t>maa://30764 (87.72)</t>
         </is>
       </c>
       <c r="E14" s="1" t="n"/>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>maa://26245 (96.75), maa://21288 (96.3), maa://39841 (94.55), maa://36682 (97.44)</t>
+          <t>maa://26245 (96.75), maa://21288 (96.3), maa://39841 (94.59), maa://36682 (97.44)</t>
         </is>
       </c>
       <c r="M14" s="1" t="n"/>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>*maa://22743 (78.04), maa://22734 (84.17), *maa://30808 (64.18), **maa://36048 (46.77), maa://45058 (93.33)</t>
+          <t>*maa://22743 (78.04), maa://22734 (84.17), *maa://30808 (64.18), **maa://36048 (47.62), maa://45058 (93.33)</t>
         </is>
       </c>
       <c r="E15" s="1" t="n"/>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>maa://24762 (90.36), *maa://22727 (70.0)</t>
+          <t>maa://24762 (90.42), *maa://22727 (70.0)</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n"/>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AF15" s="2" t="inlineStr">
         <is>
-          <t>maa://21364 (80.84), *maa://36666 (77.68), *maa://22766 (68.64)</t>
+          <t>maa://21364 (80.9), *maa://36666 (77.68), *maa://22766 (68.64)</t>
         </is>
       </c>
       <c r="AG15" s="1" t="n"/>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>maa://21441 (96.41), maa://36679 (94.55), maa://37650 (97.3)</t>
+          <t>maa://21441 (96.41), maa://36679 (94.55), maa://37650 (97.37)</t>
         </is>
       </c>
       <c r="E16" s="1" t="n"/>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>maa://26228 (95.96)</t>
+          <t>maa://26228 (96.0)</t>
         </is>
       </c>
       <c r="AC16" s="1" t="n"/>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AF16" s="2" t="inlineStr">
         <is>
-          <t>*maa://23911 (65.09), maa://27755 (93.55)</t>
+          <t>*maa://23911 (65.09), maa://27755 (93.62)</t>
         </is>
       </c>
       <c r="AG16" s="1" t="n"/>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>**maa://42324 (50.0)</t>
+          <t>*maa://42324 (51.61)</t>
         </is>
       </c>
       <c r="U17" s="1" t="n"/>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>maa://24570 (96.93)</t>
+          <t>maa://24570 (96.94)</t>
         </is>
       </c>
       <c r="E18" s="1" t="n"/>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>maa://22466 (90.53), *maa://22732 (50.54)</t>
+          <t>maa://22466 (90.59), *maa://22732 (50.54)</t>
         </is>
       </c>
       <c r="M18" s="1" t="n"/>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>maa://24385 (97.3)</t>
+          <t>maa://24385 (97.37)</t>
         </is>
       </c>
       <c r="U18" s="1" t="n"/>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>maa://24393 (97.92)</t>
+          <t>maa://24393 (97.96)</t>
         </is>
       </c>
       <c r="AC18" s="1" t="n"/>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>*maa://30709 (65.91), *maa://36668 (57.5)</t>
+          <t>*maa://30709 (66.06), *maa://36668 (57.5)</t>
         </is>
       </c>
       <c r="AC19" s="1" t="n"/>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>maa://21432 (90.34), maa://25198 (93.64), *maa://20795 (50.77), maa://36680 (91.18)</t>
+          <t>maa://21432 (90.34), maa://25198 (93.69), *maa://20795 (50.77), maa://36680 (91.18)</t>
         </is>
       </c>
       <c r="E20" s="1" t="n"/>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>maa://41331 (85.44)</t>
+          <t>maa://41331 (85.62)</t>
         </is>
       </c>
       <c r="M20" s="1" t="n"/>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>maa://21443 (81.12), ***maa://23820 (30.0)</t>
+          <t>maa://21443 (81.17), ***maa://23820 (30.0)</t>
         </is>
       </c>
       <c r="AC21" s="1" t="n"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>maa://39756 (95.81), maa://39875 (94.52)</t>
+          <t>maa://39756 (95.83), maa://39875 (94.52)</t>
         </is>
       </c>
       <c r="M23" s="1" t="n"/>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>maa://30587 (92.0), *maa://29748 (75.97), ***maa://29785 (16.18), *maa://37566 (76.92)</t>
+          <t>maa://30587 (92.0), *maa://29748 (75.97), ***maa://29785 (16.18), *maa://37566 (77.5)</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n"/>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>maa://29988 (84.11), maa://23504 (93.24), **maa://22892 (40.14), *maa://25141 (77.1), *maa://36663 (76.92), ***maa://22815 (23.08)</t>
+          <t>maa://29988 (84.11), maa://23504 (93.27), **maa://22892 (40.14), *maa://25141 (77.1), *maa://36663 (77.22), ***maa://22815 (23.08)</t>
         </is>
       </c>
       <c r="Y24" s="1" t="n"/>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>*maa://29063 (73.33), *maa://25311 (74.29), ***maa://22725 (4.84), *maa://45047 (62.5)</t>
+          <t>*maa://29063 (73.49), *maa://25311 (74.53), ***maa://22725 (4.84), *maa://45047 (62.5)</t>
         </is>
       </c>
       <c r="I25" s="1" t="n"/>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>maa://24913 (92.22)</t>
+          <t>maa://24913 (91.21)</t>
         </is>
       </c>
       <c r="I26" s="1" t="n"/>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>maa://42235 (94.23)</t>
+          <t>maa://42235 (94.44)</t>
         </is>
       </c>
       <c r="AC26" s="1" t="n"/>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AF26" s="2" t="inlineStr">
         <is>
-          <t>maa://30511 (80.95), *maa://29760 (60.0)</t>
+          <t>maa://30511 (81.4), *maa://29760 (60.0)</t>
         </is>
       </c>
       <c r="AG26" s="1" t="n"/>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>maa://24465 (90.96), maa://25725 (83.91)</t>
+          <t>maa://24465 (90.97), maa://25725 (83.91)</t>
         </is>
       </c>
       <c r="E28" s="1" t="n"/>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>maa://30770 (81.25)</t>
+          <t>maa://30770 (81.63)</t>
         </is>
       </c>
       <c r="M28" s="1" t="n"/>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>maa://39929 (90.68), maa://41749 (90.91), ***maa://39723 (13.89)</t>
+          <t>maa://39929 (90.68), maa://41749 (91.11), ***maa://39723 (13.89)</t>
         </is>
       </c>
       <c r="Y28" s="1" t="n"/>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AF28" s="2" t="inlineStr">
         <is>
-          <t>maa://36660 (92.37), *maa://36701 (66.67)</t>
+          <t>maa://36660 (92.44), *maa://36701 (66.67)</t>
         </is>
       </c>
       <c r="AG28" s="1" t="n"/>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>maa://28432 (93.55), maa://28440 (80.36), maa://31400 (98.82), *maa://28650 (71.43)</t>
+          <t>maa://28432 (93.55), maa://28440 (80.53), maa://31400 (98.82), *maa://28650 (71.43)</t>
         </is>
       </c>
       <c r="M29" s="1" t="n"/>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>maa://39477 (90.0)</t>
+          <t>maa://39477 (90.48)</t>
         </is>
       </c>
       <c r="Y30" s="1" t="n"/>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>maa://42979 (97.04), maa://45822 (100.0), *maa://45045 (80.0)</t>
+          <t>maa://42979 (97.06), maa://45822 (100.0), *maa://45045 (80.0)</t>
         </is>
       </c>
       <c r="AC30" s="1" t="n"/>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>maa://35926 (93.52), maa://36258 (84.75), *maa://43904 (72.73)</t>
+          <t>maa://35926 (93.54), maa://36258 (84.87), *maa://43904 (72.73)</t>
         </is>
       </c>
       <c r="M31" s="1" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>maa://42859 (96.0), maa://41108 (88.0), maa://41238 (97.14), maa://45523 (100.0)</t>
+          <t>maa://42859 (96.03), maa://41108 (88.0), maa://41238 (97.17), maa://45523 (100.0)</t>
         </is>
       </c>
       <c r="U32" s="1" t="n"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>maa://41296 (96.34)</t>
+          <t>maa://41296 (96.39)</t>
         </is>
       </c>
       <c r="M35" s="1" t="n"/>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>maa://45718 (98.01), *maa://47069 (73.33), maa://45789 (100.0)</t>
+          <t>maa://45718 (98.08), *maa://47069 (73.33), maa://45789 (100.0)</t>
         </is>
       </c>
       <c r="M37" s="1" t="n"/>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>maa://21280 (89.5), *maa://21239 (66.67)</t>
+          <t>maa://21280 (89.55), *maa://21239 (66.67)</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n"/>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AF38" s="2" t="inlineStr">
         <is>
-          <t>maa://36697 (86.45)</t>
+          <t>maa://36697 (86.51)</t>
         </is>
       </c>
       <c r="AG38" s="1" t="n"/>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>maa://45788 (82.18), maa://47079 (94.12), *maa://45790 (76.92)</t>
+          <t>maa://45788 (81.55), maa://47079 (91.3), *maa://45790 (71.43)</t>
         </is>
       </c>
       <c r="U39" s="1" t="n"/>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>maa://23278 (95.57), maa://21386 (95.77), maa://36664 (89.29), maa://45550 (100.0)</t>
+          <t>maa://23278 (95.58), maa://21386 (95.77), maa://36664 (89.29), maa://45550 (100.0)</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n"/>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>maa://24466 (93.48)</t>
+          <t>maa://24466 (93.75)</t>
         </is>
       </c>
       <c r="I41" s="1" t="n"/>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>maa://35931 (91.95), maa://43901 (93.1)</t>
+          <t>maa://35931 (91.98), maa://43901 (93.1)</t>
         </is>
       </c>
       <c r="I46" s="1" t="n"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>maa://32534 (94.12), **maa://32434 (33.33)</t>
+          <t>maa://32534 (94.15), **maa://32434 (33.33)</t>
         </is>
       </c>
       <c r="I53" s="1" t="n"/>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>maa://32532 (91.96)</t>
+          <t>maa://32532 (91.99)</t>
         </is>
       </c>
       <c r="I55" s="1" t="n"/>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>maa://42981 (95.12), maa://43903 (100.0)</t>
+          <t>maa://42981 (95.24), maa://43903 (100.0)</t>
         </is>
       </c>
       <c r="I62" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单作者版.xlsx
+++ b/Excel/悖论模拟干员名单作者版.xlsx
@@ -1429,7 +1429,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.20 13:18:45</t>
+          <t>更新日期：2025.03.21 13:18:27</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>*maa://21248 (73.55), **maa://22728 (46.67)</t>
+          <t>*maa://21248 (73.77), **maa://22728 (46.67)</t>
         </is>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>maa://26245 (96.77), maa://21288 (96.3), maa://39841 (94.69), maa://36682 (97.44)</t>
+          <t>maa://26245 (96.77), maa://21288 (96.3), maa://39841 (93.91), maa://36682 (97.44)</t>
         </is>
       </c>
       <c r="M14" s="1" t="n"/>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AF15" s="2" t="inlineStr">
         <is>
-          <t>maa://21364 (81.07), *maa://36666 (77.39), *maa://22766 (68.64)</t>
+          <t>maa://21364 (81.07), *maa://36666 (77.39), *maa://22766 (68.07)</t>
         </is>
       </c>
       <c r="AG15" s="1" t="n"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>*maa://24368 (78.44), *maa://46650 (62.5)</t>
+          <t>*maa://24368 (78.5), *maa://46650 (62.5)</t>
         </is>
       </c>
       <c r="E24" s="1" t="n"/>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>maa://29988 (84.17), maa://23504 (93.33), **maa://22892 (40.14), *maa://25141 (77.1), *maa://36663 (77.5), ***maa://22815 (23.08)</t>
+          <t>maa://29988 (83.85), maa://23504 (93.33), **maa://22892 (40.14), *maa://25141 (77.1), *maa://36663 (77.5), ***maa://22815 (23.08)</t>
         </is>
       </c>
       <c r="Y24" s="1" t="n"/>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>*maa://29063 (73.05), *maa://25311 (74.77), ***maa://22725 (4.76), *maa://45047 (62.5)</t>
+          <t>*maa://29063 (72.62), *maa://25311 (74.77), ***maa://22725 (4.76), *maa://45047 (62.5)</t>
         </is>
       </c>
       <c r="I25" s="1" t="n"/>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>maa://28432 (93.57), maa://28440 (80.53), maa://31400 (98.82), *maa://28650 (71.43)</t>
+          <t>maa://28432 (93.59), maa://28440 (80.53), maa://31400 (98.82), *maa://28650 (71.43)</t>
         </is>
       </c>
       <c r="M29" s="1" t="n"/>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>maa://21895 (97.06), maa://36667 (97.7), **maa://20793 (38.78), maa://22760 (100.0)</t>
+          <t>maa://21895 (97.06), maa://36667 (97.73), **maa://20793 (38.78), maa://22760 (100.0)</t>
         </is>
       </c>
       <c r="I32" s="1" t="n"/>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>maa://36670 (89.22), maa://25199 (84.82), maa://30434 (91.86), maa://45059 (80.95), ***maa://25036 (19.23), *maa://44165 (66.67)</t>
+          <t>maa://36670 (89.22), maa://25199 (84.82), maa://30434 (91.86), maa://45059 (81.82), ***maa://25036 (19.23), *maa://44165 (66.67)</t>
         </is>
       </c>
       <c r="I39" s="1" t="n"/>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>maa://27410 (96.49), maa://29661 (97.32), maa://28038 (84.62)</t>
+          <t>maa://27410 (96.49), maa://29661 (97.33), maa://28038 (84.62)</t>
         </is>
       </c>
       <c r="I47" s="1" t="n"/>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>maa://32532 (92.04)</t>
+          <t>maa://32532 (92.06)</t>
         </is>
       </c>
       <c r="I55" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单作者版.xlsx
+++ b/Excel/悖论模拟干员名单作者版.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>maa://40192 (96.67), maa://36987 (96.15), maa://39849 (88.89)</t>
+          <t>maa://40192 (96.72), maa://36987 (96.15), maa://39849 (88.89)</t>
         </is>
       </c>
       <c r="E3" s="1" t="n"/>
@@ -1429,7 +1429,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.28 13:20:26</t>
+          <t>更新日期：2025.03.29 13:18:03</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="AF9" s="2" t="inlineStr">
         <is>
-          <t>maa://26206 (88.19), *maa://22865 (51.85)</t>
+          <t>maa://26206 (88.28), *maa://22865 (51.85)</t>
         </is>
       </c>
       <c r="AG9" s="1" t="n"/>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>maa://22747 (92.59), maa://22501 (97.83), maa://45521 (85.71)</t>
+          <t>maa://22747 (92.59), maa://22501 (97.83), maa://45521 (86.36)</t>
         </is>
       </c>
       <c r="U11" s="1" t="n"/>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>maa://23669 (95.52), maa://36677 (94.12), maa://39872 (92.0)</t>
+          <t>maa://23669 (95.53), maa://36677 (94.12), maa://39872 (92.0)</t>
         </is>
       </c>
       <c r="AC12" s="1" t="n"/>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>maa://24999 (92.14), maa://36673 (92.41), maa://25001 (85.92)</t>
+          <t>maa://24999 (92.15), maa://36673 (92.41), maa://25001 (85.92)</t>
         </is>
       </c>
       <c r="E13" s="1" t="n"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>*maa://21248 (74.09), **maa://22728 (46.67)</t>
+          <t>*maa://21248 (74.19), **maa://22728 (46.67)</t>
         </is>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>maa://24570 (96.98)</t>
+          <t>maa://24570 (97.0)</t>
         </is>
       </c>
       <c r="E18" s="1" t="n"/>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>maa://22466 (90.75), *maa://22732 (51.04)</t>
+          <t>maa://22466 (90.75), *maa://22732 (51.55)</t>
         </is>
       </c>
       <c r="M18" s="1" t="n"/>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>maa://29652 (97.67)</t>
+          <t>maa://29652 (97.73)</t>
         </is>
       </c>
       <c r="AC23" s="1" t="n"/>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>*maa://29765 (64.37), maa://23263 (95.28)</t>
+          <t>*maa://29765 (64.77), maa://23263 (95.28)</t>
         </is>
       </c>
       <c r="U28" s="1" t="n"/>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>maa://39929 (90.89), maa://41749 (91.4), ***maa://39723 (13.89)</t>
+          <t>maa://39929 (90.89), maa://41749 (91.49), ***maa://39723 (13.89)</t>
         </is>
       </c>
       <c r="Y28" s="1" t="n"/>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>maa://48817 (90.91)</t>
+          <t>maa://48817 (84.62)</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n"/>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>maa://45718 (97.6), *maa://47069 (73.33), maa://45789 (100.0)</t>
+          <t>maa://45718 (97.6), *maa://47069 (75.0), maa://45789 (100.0)</t>
         </is>
       </c>
       <c r="M37" s="1" t="n"/>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>maa://36670 (89.22), maa://25199 (84.82), maa://30434 (92.05), maa://45059 (81.82), ***maa://25036 (19.23), *maa://44165 (66.67)</t>
+          <t>maa://36670 (89.22), maa://25199 (84.82), maa://30434 (92.22), maa://45059 (81.82), ***maa://25036 (19.23), *maa://44165 (66.67)</t>
         </is>
       </c>
       <c r="I39" s="1" t="n"/>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>maa://45788 (80.77), maa://47079 (92.59), *maa://45790 (73.33)</t>
+          <t>maa://45788 (80.77), maa://47079 (93.1), *maa://45790 (73.33)</t>
         </is>
       </c>
       <c r="U39" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单作者版.xlsx
+++ b/Excel/悖论模拟干员名单作者版.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>*maa://24633 (56.17), *maa://30515 (70.48), maa://39402 (93.42), *maa://34787 (72.5), ***maa://20792 (11.93), ***maa://29083 (27.78)</t>
+          <t>*maa://24633 (56.17), *maa://30515 (70.48), maa://39402 (93.51), *maa://34787 (72.5), ***maa://20792 (11.93), ***maa://29083 (27.78)</t>
         </is>
       </c>
       <c r="M2" s="1" t="n"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>maa://21246 (91.53), maa://36684 (94.57), ***maa://22731 (6.25)</t>
+          <t>maa://21246 (91.55), maa://36684 (94.57), ***maa://22731 (6.25)</t>
         </is>
       </c>
       <c r="AC2" s="1" t="n"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>maa://25251 (91.27), ***maa://21730 (27.27), ***maa://39501 (13.89), **maa://36675 (50.0)</t>
+          <t>maa://25251 (91.27), ***maa://21730 (26.92), ***maa://39501 (13.89), **maa://36675 (50.0)</t>
         </is>
       </c>
       <c r="AG2" s="1" t="n"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>maa://21247 (98.65), *maa://22748 (60.0)</t>
+          <t>maa://21247 (98.21), *maa://22748 (60.0)</t>
         </is>
       </c>
       <c r="I3" s="1" t="n"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>maa://21249 (94.51), maa://26254 (96.77), **maa://22738 (50.0)</t>
+          <t>maa://21249 (94.19), maa://26254 (96.77), **maa://22738 (50.0)</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n"/>
@@ -914,7 +914,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>maa://24632 (93.89), **maa://24303 (38.46), maa://22499 (86.67), maa://22746 (100.0)</t>
+          <t>maa://24632 (93.92), **maa://24303 (38.46), maa://22499 (86.67), maa://22746 (100.0)</t>
         </is>
       </c>
       <c r="E4" s="1" t="n"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>maa://49983 (94.44), maa://50121 (100.0)</t>
+          <t>maa://49983 (90.48), maa://50121 (83.33)</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>**maa://32495 (48.54), ***maa://31785 (22.22), maa://43217 (90.8), ***maa://36683 (29.79)</t>
+          <t>**maa://32495 (48.73), ***maa://31785 (22.22), maa://43217 (90.8), ***maa://36683 (29.79)</t>
         </is>
       </c>
       <c r="Y4" s="1" t="n"/>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="AE4" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
-          <t>*maa://30062 (64.71), *maa://39394 (65.38), ***maa://26209 (13.04), maa://48095 (100.0)</t>
+          <t>*maa://30062 (64.71), *maa://39394 (65.38), ***maa://26209 (13.04)</t>
         </is>
       </c>
       <c r="AG4" s="1" t="n"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>maa://21245 (84.92), maa://22744 (81.48)</t>
+          <t>maa://21245 (85.04), maa://22744 (81.48)</t>
         </is>
       </c>
       <c r="E5" s="1" t="n"/>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>maa://21919 (96.61), *maa://21281 (80.0)</t>
+          <t>maa://21919 (96.67), *maa://21281 (80.0)</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n"/>
@@ -1429,7 +1429,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.04.17 13:19:49</t>
+          <t>更新日期：2025.04.19 13:19:27</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>maa://21411 (96.11)</t>
+          <t>maa://21411 (96.13)</t>
         </is>
       </c>
       <c r="Y8" s="1" t="n"/>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>maa://26223 (98.01)</t>
+          <t>maa://26223 (98.03)</t>
         </is>
       </c>
       <c r="Y9" s="1" t="n"/>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>maa://28711 (87.3), **maa://39938 (46.67), **maa://27377 (42.86), ***maa://25174 (19.05), *maa://45044 (66.67), maa://40166 (96.67)</t>
+          <t>maa://28711 (87.3), **maa://39938 (45.16), **maa://27377 (42.86), ***maa://25174 (19.05), *maa://45044 (66.67), maa://40166 (96.88)</t>
         </is>
       </c>
       <c r="AC9" s="1" t="n"/>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="AF9" s="2" t="inlineStr">
         <is>
-          <t>maa://26206 (87.88), *maa://22865 (51.85)</t>
+          <t>maa://26206 (88.06), *maa://22865 (51.85)</t>
         </is>
       </c>
       <c r="AG9" s="1" t="n"/>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>***maa://25695 (18.65), ***maa://39951 (12.7), ***maa://34206 (22.22), *maa://45271 (54.17), ***maa://39243 (25.0)</t>
+          <t>***maa://25695 (18.65), ***maa://39951 (12.7), ***maa://34206 (22.22), *maa://45271 (56.0), ***maa://39243 (25.0)</t>
         </is>
       </c>
       <c r="E10" s="1" t="n"/>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AF10" s="2" t="inlineStr">
         <is>
-          <t>*maa://25021 (54.0), *maa://22733 (62.16), **maa://22761 (50.0)</t>
+          <t>*maa://25021 (53.47), *maa://22733 (62.16), **maa://22761 (50.0)</t>
         </is>
       </c>
       <c r="AG10" s="1" t="n"/>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>maa://29912 (97.4), maa://22516 (88.37), *maa://20794 (51.47)</t>
+          <t>maa://29912 (97.44), maa://22516 (88.37), *maa://20794 (52.17)</t>
         </is>
       </c>
       <c r="AC11" s="1" t="n"/>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>maa://21867 (90.17), **maa://45826 (33.33)</t>
+          <t>maa://21867 (90.23), **maa://45826 (33.33)</t>
         </is>
       </c>
       <c r="I12" s="1" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>maa://22753 (90.86), *maa://21485 (74.83), maa://37962 (91.84)</t>
+          <t>maa://22753 (90.91), *maa://21485 (74.83), maa://37962 (92.16)</t>
         </is>
       </c>
       <c r="Y12" s="1" t="n"/>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="AF12" s="2" t="inlineStr">
         <is>
-          <t>*maa://28932 (78.21), *maa://20106 (63.96), *maa://22769 (64.29)</t>
+          <t>*maa://28932 (78.34), *maa://20106 (63.96), *maa://22769 (64.29)</t>
         </is>
       </c>
       <c r="AG12" s="1" t="n"/>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>maa://24999 (92.33), maa://36673 (92.68), maa://25001 (85.92)</t>
+          <t>maa://24999 (92.36), maa://36673 (92.68), maa://25001 (85.92)</t>
         </is>
       </c>
       <c r="E13" s="1" t="n"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>*maa://21248 (73.33), **maa://22728 (46.67)</t>
+          <t>*maa://21248 (73.54), **maa://22728 (46.67)</t>
         </is>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="AF13" s="2" t="inlineStr">
         <is>
-          <t>**maa://22737 (34.69), maa://39883 (90.36), *maa://39885 (53.12)</t>
+          <t>**maa://22737 (35.57), maa://39883 (90.36), *maa://39885 (53.12)</t>
         </is>
       </c>
       <c r="AG13" s="1" t="n"/>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>*maa://22743 (78.73), maa://22734 (84.17), *maa://30808 (64.18), *maa://36048 (56.0), maa://45058 (93.75)</t>
+          <t>*maa://22743 (78.73), maa://22734 (84.17), *maa://30808 (64.18), *maa://36048 (57.14), maa://45058 (93.75)</t>
         </is>
       </c>
       <c r="E15" s="1" t="n"/>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AF15" s="2" t="inlineStr">
         <is>
-          <t>maa://21364 (80.52), *maa://36666 (78.05), *maa://22766 (68.33)</t>
+          <t>maa://21364 (80.52), *maa://36666 (78.23), *maa://22766 (68.33)</t>
         </is>
       </c>
       <c r="AG15" s="1" t="n"/>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AF16" s="2" t="inlineStr">
         <is>
-          <t>*maa://23911 (66.06), maa://27755 (93.68)</t>
+          <t>*maa://23911 (66.36), maa://27755 (93.68)</t>
         </is>
       </c>
       <c r="AG16" s="1" t="n"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>maa://24421 (88.12)</t>
+          <t>maa://24421 (87.79)</t>
         </is>
       </c>
       <c r="I18" s="1" t="n"/>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>maa://24386 (99.22)</t>
+          <t>maa://24386 (99.23)</t>
         </is>
       </c>
       <c r="U19" s="1" t="n"/>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>*maa://30709 (66.37), *maa://36668 (58.02)</t>
+          <t>*maa://30709 (66.45), *maa://36668 (58.02)</t>
         </is>
       </c>
       <c r="AC19" s="1" t="n"/>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>*maa://49976 (80.0), maa://50085 (83.33)</t>
+          <t>maa://49976 (81.08), maa://50085 (83.33)</t>
         </is>
       </c>
       <c r="Y20" s="1" t="n"/>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AF21" s="2" t="inlineStr">
         <is>
-          <t>maa://22524 (92.64), *maa://22432 (77.78)</t>
+          <t>maa://22524 (92.64), *maa://22432 (78.26)</t>
         </is>
       </c>
       <c r="AG21" s="1" t="n"/>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>maa://25236 (95.79), **maa://21678 (48.94), **maa://22735 (42.86)</t>
+          <t>maa://25236 (95.83), **maa://21678 (48.94), **maa://22735 (42.86)</t>
         </is>
       </c>
       <c r="I22" s="1" t="n"/>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>maa://21282 (98.68), *maa://37649 (66.67)</t>
+          <t>maa://21282 (98.68), *maa://37649 (67.74)</t>
         </is>
       </c>
       <c r="Y22" s="1" t="n"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>maa://39756 (95.9), maa://39875 (94.59)</t>
+          <t>maa://39756 (95.65), maa://39875 (94.59)</t>
         </is>
       </c>
       <c r="M23" s="1" t="n"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>*maa://24368 (78.52), *maa://46650 (58.33)</t>
+          <t>*maa://24368 (78.57), *maa://46650 (53.85)</t>
         </is>
       </c>
       <c r="E24" s="1" t="n"/>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>maa://29988 (83.46), maa://23504 (93.51), **maa://22892 (40.67), *maa://25141 (77.27), *maa://36663 (78.31), ***maa://22815 (23.08)</t>
+          <t>maa://29988 (83.46), maa://23504 (93.53), **maa://22892 (41.06), *maa://25141 (77.27), *maa://36663 (78.57), ***maa://22815 (23.08)</t>
         </is>
       </c>
       <c r="Y24" s="1" t="n"/>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AF24" s="2" t="inlineStr">
         <is>
-          <t>maa://22523 (84.8), *maa://36672 (79.31), maa://29910 (93.44), **maa://21440 (35.71), maa://45831 (87.5)</t>
+          <t>maa://22523 (84.88), *maa://36672 (79.31), maa://29910 (93.55), **maa://21440 (35.71), maa://45831 (88.89)</t>
         </is>
       </c>
       <c r="AG24" s="1" t="n"/>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>maa://29753 (95.34)</t>
+          <t>maa://29753 (95.36)</t>
         </is>
       </c>
       <c r="E25" s="1" t="n"/>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AF26" s="2" t="inlineStr">
         <is>
-          <t>maa://30511 (82.22), *maa://29760 (56.25)</t>
+          <t>maa://30511 (80.43), *maa://29760 (56.25)</t>
         </is>
       </c>
       <c r="AG26" s="1" t="n"/>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>maa://24465 (91.03), maa://25725 (84.62)</t>
+          <t>maa://24465 (90.91), maa://25725 (84.62)</t>
         </is>
       </c>
       <c r="E28" s="1" t="n"/>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AF28" s="2" t="inlineStr">
         <is>
-          <t>maa://36660 (92.27), *maa://36701 (66.67)</t>
+          <t>maa://36660 (92.31), *maa://36701 (66.67)</t>
         </is>
       </c>
       <c r="AG28" s="1" t="n"/>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>maa://28432 (93.66), maa://28440 (81.36), maa://31400 (98.84), *maa://28650 (71.43)</t>
+          <t>maa://28432 (93.66), maa://28440 (81.67), maa://31400 (98.84), *maa://28650 (71.43)</t>
         </is>
       </c>
       <c r="M29" s="1" t="n"/>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AF29" s="2" t="inlineStr">
         <is>
-          <t>*maa://24080 (69.01), maa://42865 (81.08), ***maa://34960 (8.33)</t>
+          <t>*maa://24080 (69.01), maa://42865 (81.58), ***maa://34960 (8.33)</t>
         </is>
       </c>
       <c r="AG29" s="1" t="n"/>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>maa://35926 (93.51), maa://36258 (85.27), *maa://43904 (76.92)</t>
+          <t>maa://35926 (93.51), maa://36258 (85.38), *maa://43904 (76.92)</t>
         </is>
       </c>
       <c r="M31" s="1" t="n"/>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>maa://21895 (97.21), maa://36667 (97.83), **maa://20793 (38.78), maa://22760 (100.0)</t>
+          <t>maa://21895 (97.22), maa://36667 (97.85), **maa://20793 (38.78), maa://22760 (100.0)</t>
         </is>
       </c>
       <c r="I32" s="1" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>maa://42859 (96.5), maa://41108 (88.0), maa://41238 (97.35), maa://45523 (100.0)</t>
+          <t>maa://42859 (96.5), maa://41108 (88.0), maa://41238 (97.37), maa://45523 (100.0)</t>
         </is>
       </c>
       <c r="U32" s="1" t="n"/>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>maa://21956 (80.92), *maa://22730 (76.67)</t>
+          <t>maa://21956 (81.05), *maa://22730 (76.67)</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n"/>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>maa://48817 (93.1)</t>
+          <t>maa://48817 (93.33)</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>maa://24526 (92.45)</t>
+          <t>maa://24526 (92.48)</t>
         </is>
       </c>
       <c r="U34" s="1" t="n"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>maa://41296 (96.74)</t>
+          <t>maa://41296 (96.76)</t>
         </is>
       </c>
       <c r="M35" s="1" t="n"/>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>maa://45718 (97.8), *maa://47069 (76.47), maa://45789 (100.0)</t>
+          <t>maa://45718 (97.81), *maa://47069 (76.47), maa://45789 (100.0)</t>
         </is>
       </c>
       <c r="M37" s="1" t="n"/>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>maa://21280 (89.69), *maa://21239 (69.23)</t>
+          <t>maa://21280 (89.73), *maa://21239 (69.23)</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n"/>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>maa://36670 (89.22), maa://25199 (85.09), maa://30434 (91.67), maa://45059 (80.77), ***maa://25036 (18.52), *maa://44165 (66.67)</t>
+          <t>maa://36670 (89.32), maa://25199 (85.09), maa://30434 (91.75), maa://45059 (81.48), ***maa://25036 (18.52), *maa://44165 (66.67)</t>
         </is>
       </c>
       <c r="I39" s="1" t="n"/>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>*maa://45788 (78.5), maa://47079 (92.68), *maa://45790 (70.59)</t>
+          <t>*maa://45788 (78.5), maa://47079 (92.86), *maa://45790 (70.59)</t>
         </is>
       </c>
       <c r="U39" s="1" t="n"/>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>maa://35931 (92.15), maa://43901 (94.29)</t>
+          <t>maa://35931 (92.17), maa://43901 (94.29)</t>
         </is>
       </c>
       <c r="I46" s="1" t="n"/>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>maa://27410 (96.58), maa://29661 (97.37), maa://28038 (84.62)</t>
+          <t>maa://27410 (96.59), maa://29661 (97.39), maa://28038 (84.62)</t>
         </is>
       </c>
       <c r="I47" s="1" t="n"/>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>maa://32532 (92.42)</t>
+          <t>maa://32532 (92.45)</t>
         </is>
       </c>
       <c r="I55" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单作者版.xlsx
+++ b/Excel/悖论模拟干员名单作者版.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>maa://25390 (95.33), maa://24702 (94.81), maa://36681 (86.42)</t>
+          <t>maa://25390 (95.41), maa://24702 (94.82), maa://36681 (86.42)</t>
         </is>
       </c>
       <c r="E2" s="1" t="n"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>maa://39402 (94.59), *maa://24633 (56.02), *maa://30515 (70.37), *maa://34787 (73.33), ***maa://20792 (11.93), ***maa://29083 (27.78), **maa://54304 (50.0)</t>
+          <t>maa://39402 (94.78), *maa://24633 (56.02), *maa://30515 (70.37), *maa://34787 (73.63), ***maa://20792 (11.93), ***maa://29083 (27.78), *maa://54304 (55.56)</t>
         </is>
       </c>
       <c r="M2" s="1" t="n"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>maa://22742 (91.04), *maa://20791 (62.65)</t>
+          <t>maa://22742 (91.26), *maa://20791 (62.65)</t>
         </is>
       </c>
       <c r="U2" s="1" t="n"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>maa://21246 (91.45), maa://36684 (93.59), ***maa://22731 (6.25)</t>
+          <t>maa://21246 (91.45), maa://36684 (92.99), ***maa://22731 (6.25)</t>
         </is>
       </c>
       <c r="AC2" s="1" t="n"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>maa://40192 (96.97), maa://36987 (96.15), maa://39849 (88.89)</t>
+          <t>maa://40192 (97.03), maa://36987 (96.15), maa://39849 (88.89)</t>
         </is>
       </c>
       <c r="E3" s="1" t="n"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>maa://21247 (98.42), *maa://22748 (60.0)</t>
+          <t>maa://21247 (98.43), *maa://22748 (60.0)</t>
         </is>
       </c>
       <c r="I3" s="1" t="n"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>*maa://22880 (65.79), maa://20276 (88.29), *maa://22749 (75.0)</t>
+          <t>*maa://22880 (65.94), maa://20276 (88.46), *maa://22749 (75.0)</t>
         </is>
       </c>
       <c r="M3" s="1" t="n"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>maa://21249 (94.62), maa://26254 (97.22), **maa://22738 (50.0)</t>
+          <t>maa://21249 (94.64), maa://26254 (97.22), *maa://22738 (66.67)</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>maa://24617 (90.84), maa://45854 (83.54), **maa://20790 (42.86), ***maa://37170 (16.44)</t>
+          <t>maa://24617 (90.91), maa://45854 (84.09), **maa://20790 (42.86), ***maa://37170 (16.44)</t>
         </is>
       </c>
       <c r="U3" s="1" t="n"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>maa://27396 (84.18), maa://27484 (96.27), maa://27480 (84.21)</t>
+          <t>maa://27396 (84.27), maa://27484 (96.32), maa://27480 (84.21)</t>
         </is>
       </c>
       <c r="Y3" s="1" t="n"/>
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>maa://24390 (95.51), maa://52241 (100.0)</t>
+          <t>maa://24390 (95.56), maa://52241 (100.0)</t>
         </is>
       </c>
       <c r="AC3" s="1" t="n"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>maa://49983 (95.38), maa://50121 (93.75)</t>
+          <t>maa://49983 (95.65), maa://50121 (94.12)</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>maa://32509 (94.66), maa://27295 (87.91), maa://22754 (89.19), *maa://31008 (79.55), *maa://21746 (54.55)</t>
+          <t>maa://32509 (93.94), maa://27295 (88.04), maa://22754 (89.19), *maa://31008 (79.55), *maa://21746 (54.55)</t>
         </is>
       </c>
       <c r="U4" s="1" t="n"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>**maa://32495 (48.76), maa://43217 (93.39), ***maa://31785 (22.22), ***maa://36683 (29.79)</t>
+          <t>**maa://32495 (48.76), maa://43217 (93.5), ***maa://31785 (22.22), ***maa://36683 (29.79)</t>
         </is>
       </c>
       <c r="Y4" s="1" t="n"/>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>*maa://32658 (76.0)</t>
+          <t>*maa://32658 (76.92)</t>
         </is>
       </c>
       <c r="AC4" s="1" t="n"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>maa://21245 (84.7), maa://22744 (81.48), maa://54105 (100.0)</t>
+          <t>maa://21245 (84.4), maa://22744 (82.14), maa://54105 (100.0)</t>
         </is>
       </c>
       <c r="E5" s="1" t="n"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>maa://24370 (96.88)</t>
+          <t>maa://24370 (96.92)</t>
         </is>
       </c>
       <c r="I6" s="1" t="n"/>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>maa://24839 (98.81)</t>
+          <t>maa://24839 (98.82)</t>
         </is>
       </c>
       <c r="M6" s="1" t="n"/>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>maa://52754 (88.89)</t>
+          <t>*maa://52754 (78.57)</t>
         </is>
       </c>
       <c r="Y6" s="1" t="n"/>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>*maa://22763 (65.71)</t>
+          <t>*maa://22763 (66.67)</t>
         </is>
       </c>
       <c r="I7" s="1" t="n"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>maa://22750 (92.73)</t>
+          <t>maa://22750 (92.98)</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n"/>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>maa://21291 (86.21)</t>
+          <t>maa://21291 (86.67)</t>
         </is>
       </c>
       <c r="U7" s="1" t="n"/>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AF7" s="2" t="inlineStr">
         <is>
-          <t>*maa://26191 (67.42), maa://45272 (96.88), *maa://36671 (69.23), *maa://42530 (62.5)</t>
+          <t>*maa://26191 (67.42), maa://45272 (96.97), *maa://36671 (69.23), *maa://42530 (62.5)</t>
         </is>
       </c>
       <c r="AG7" s="1" t="n"/>
@@ -1429,7 +1429,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.05.24 13:19:10</t>
+          <t>更新日期：2025.05.31 13:19:45</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>maa://21411 (95.96)</t>
+          <t>maa://21411 (96.05)</t>
         </is>
       </c>
       <c r="Y8" s="1" t="n"/>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>maa://25389 (90.24)</t>
+          <t>maa://25389 (90.48)</t>
         </is>
       </c>
       <c r="AC8" s="1" t="n"/>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>**maa://47450 (33.33)</t>
+          <t>**maa://47450 (50.0), maa://56348 (100.0)</t>
         </is>
       </c>
       <c r="I9" s="1" t="n"/>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>maa://22762 (92.78), maa://39552 (83.33)</t>
+          <t>maa://22762 (92.86), maa://39552 (83.33)</t>
         </is>
       </c>
       <c r="M9" s="1" t="n"/>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>maa://22736 (83.04)</t>
+          <t>maa://22736 (83.19)</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>maa://28711 (87.14), **maa://39938 (45.24), **maa://45044 (40.0), maa://40166 (94.74), **maa://27377 (42.86), ***maa://25174 (19.05)</t>
+          <t>maa://28711 (87.23), **maa://39938 (45.24), **maa://45044 (40.0), maa://40166 (93.02), **maa://27377 (42.86), ***maa://25174 (19.05)</t>
         </is>
       </c>
       <c r="AC9" s="1" t="n"/>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AF9" s="2" t="inlineStr">
         <is>
-          <t>maa://26206 (88.89), *maa://22865 (51.85)</t>
+          <t>maa://26206 (88.95), *maa://22865 (52.73)</t>
         </is>
       </c>
       <c r="AG9" s="1" t="n"/>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>***maa://25695 (18.81), ***maa://39951 (12.33), ***maa://34206 (22.22), *maa://45271 (60.0), ***maa://39243 (25.0), maa://54000 (100.0)</t>
+          <t>***maa://25695 (18.72), ***maa://39951 (12.33), ***maa://34206 (22.22), *maa://45271 (59.72), ***maa://39243 (25.0), maa://54000 (100.0)</t>
         </is>
       </c>
       <c r="E10" s="1" t="n"/>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>maa://27395 (96.64), maa://22755 (88.89), **maa://22756 (40.91), ***maa://21737 (11.76)</t>
+          <t>maa://27395 (96.68), maa://22755 (88.98), **maa://22756 (40.91), ***maa://21737 (11.76)</t>
         </is>
       </c>
       <c r="U10" s="1" t="n"/>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>maa://22301 (97.89), maa://45828 (93.18), maa://22726 (100.0)</t>
+          <t>maa://22301 (97.89), maa://45828 (93.33), maa://22726 (100.0)</t>
         </is>
       </c>
       <c r="Y10" s="1" t="n"/>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AF10" s="2" t="inlineStr">
         <is>
-          <t>*maa://25021 (53.85), *maa://22733 (65.0), **maa://22761 (50.0)</t>
+          <t>*maa://25021 (53.85), *maa://22733 (65.85), **maa://22761 (50.0)</t>
         </is>
       </c>
       <c r="AG10" s="1" t="n"/>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>maa://36707 (99.37)</t>
+          <t>maa://36707 (99.38)</t>
         </is>
       </c>
       <c r="E11" s="1" t="n"/>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>maa://22747 (90.8), maa://22501 (98.15), maa://45521 (91.43)</t>
+          <t>maa://22747 (90.8), maa://22501 (98.2), maa://45521 (91.43)</t>
         </is>
       </c>
       <c r="U11" s="1" t="n"/>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>maa://36713 (98.1)</t>
+          <t>maa://36713 (98.13)</t>
         </is>
       </c>
       <c r="Y11" s="1" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>maa://29912 (97.78), maa://22516 (87.36), *maa://20794 (55.84)</t>
+          <t>maa://29912 (97.78), maa://22516 (87.36), *maa://20794 (56.41)</t>
         </is>
       </c>
       <c r="AC11" s="1" t="n"/>
@@ -2010,11 +2010,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="1" t="n"/>
       <c r="R12" s="1" t="inlineStr">
         <is>
@@ -2044,7 +2040,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>maa://22753 (91.83), *maa://21485 (75.84), maa://37962 (91.8)</t>
+          <t>maa://22753 (91.83), *maa://21485 (75.84), maa://37962 (92.06)</t>
         </is>
       </c>
       <c r="Y12" s="1" t="n"/>
@@ -2060,7 +2056,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>maa://23669 (95.64), maa://36677 (95.18), maa://39872 (93.1)</t>
+          <t>maa://23669 (95.64), maa://36677 (95.24), maa://39872 (93.1)</t>
         </is>
       </c>
       <c r="AC12" s="1" t="n"/>
@@ -2076,7 +2072,7 @@
       </c>
       <c r="AF12" s="2" t="inlineStr">
         <is>
-          <t>*maa://28932 (79.19), *maa://20106 (64.29), *maa://22769 (64.29)</t>
+          <t>*maa://28932 (78.86), *maa://20106 (64.29), *maa://22769 (64.29)</t>
         </is>
       </c>
       <c r="AG12" s="1" t="n"/>
@@ -2094,7 +2090,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>maa://24999 (92.7), maa://36673 (91.86), maa://25001 (86.49)</t>
+          <t>maa://24999 (92.74), maa://36673 (91.95), maa://25001 (86.49)</t>
         </is>
       </c>
       <c r="E13" s="1" t="n"/>
@@ -2110,7 +2106,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>*maa://21248 (73.45), **maa://22728 (45.65)</t>
+          <t>*maa://21248 (73.65), **maa://22728 (45.65)</t>
         </is>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -2142,7 +2138,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>maa://22676 (93.57), *maa://22583 (77.22), *maa://22500 (59.57), maa://48321 (100.0)</t>
+          <t>maa://22676 (93.66), *maa://22583 (77.78), *maa://22500 (59.57), maa://48321 (100.0)</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n"/>
@@ -2174,7 +2170,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>maa://34957 (83.02), **maa://22768 (50.0)</t>
+          <t>maa://34957 (83.33), **maa://22768 (50.0)</t>
         </is>
       </c>
       <c r="Y13" s="1" t="n"/>
@@ -2206,7 +2202,7 @@
       </c>
       <c r="AF13" s="2" t="inlineStr">
         <is>
-          <t>**maa://22737 (38.22), maa://39883 (87.6), **maa://39885 (50.0)</t>
+          <t>**maa://22737 (38.22), maa://39883 (87.8), **maa://39885 (50.0)</t>
         </is>
       </c>
       <c r="AG13" s="1" t="n"/>
@@ -2256,7 +2252,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>maa://39841 (94.16), maa://26245 (96.59), maa://21288 (96.3), maa://36682 (95.83)</t>
+          <t>maa://39841 (94.19), maa://26245 (96.63), maa://21288 (96.3), maa://36682 (95.83)</t>
         </is>
       </c>
       <c r="M14" s="1" t="n"/>
@@ -2272,7 +2268,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>maa://23250 (98.84), maa://20107 (87.1), maa://22772 (100.0), *maa://22745 (66.67)</t>
+          <t>maa://23250 (98.85), maa://20107 (87.1), maa://22772 (100.0), *maa://22745 (66.67)</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n"/>
@@ -2304,7 +2300,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>maa://37468 (91.67)</t>
+          <t>maa://37468 (92.0)</t>
         </is>
       </c>
       <c r="Y14" s="1" t="n"/>
@@ -2354,7 +2350,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>*maa://22743 (79.08), maa://22734 (84.55), *maa://30808 (65.71), *maa://36048 (67.31), maa://45058 (84.21)</t>
+          <t>*maa://22743 (79.17), maa://22734 (84.55), *maa://30808 (65.71), *maa://36048 (68.22), maa://45058 (84.21)</t>
         </is>
       </c>
       <c r="E15" s="1" t="n"/>
@@ -2370,7 +2366,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>maa://24304 (87.1), maa://21478 (90.0)</t>
+          <t>maa://24304 (87.25), maa://21478 (90.0)</t>
         </is>
       </c>
       <c r="I15" s="1" t="n"/>
@@ -2402,7 +2398,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>maa://24762 (91.21), *maa://22727 (70.0)</t>
+          <t>maa://24762 (91.26), *maa://22727 (70.0)</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n"/>
@@ -2418,7 +2414,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>maa://23892 (96.55)</t>
+          <t>maa://23892 (96.59)</t>
         </is>
       </c>
       <c r="U15" s="1" t="n"/>
@@ -2466,7 +2462,7 @@
       </c>
       <c r="AF15" s="2" t="inlineStr">
         <is>
-          <t>maa://21364 (81.1), maa://36666 (81.46), *maa://22766 (68.29)</t>
+          <t>maa://21364 (81.1), maa://36666 (81.7), *maa://22766 (68.29)</t>
         </is>
       </c>
       <c r="AG15" s="1" t="n"/>
@@ -2484,7 +2480,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>maa://21441 (96.54), maa://37650 (96.3), maa://36679 (94.55)</t>
+          <t>maa://21441 (96.54), maa://37650 (96.36), maa://36679 (94.55)</t>
         </is>
       </c>
       <c r="E16" s="1" t="n"/>
@@ -2532,7 +2528,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>maa://28504 (92.54)</t>
+          <t>maa://28504 (92.65)</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n"/>
@@ -2548,7 +2544,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>maa://22729 (94.44), *maa://28648 (73.75), *maa://36674 (80.0)</t>
+          <t>maa://22729 (94.48), *maa://28648 (73.75), *maa://36674 (80.0)</t>
         </is>
       </c>
       <c r="U16" s="1" t="n"/>
@@ -2580,7 +2576,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>maa://26228 (95.45)</t>
+          <t>maa://26228 (95.54)</t>
         </is>
       </c>
       <c r="AC16" s="1" t="n"/>
@@ -2630,7 +2626,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>maa://22430 (89.52), maa://39599 (85.53)</t>
+          <t>maa://22430 (89.67), maa://39599 (85.71)</t>
         </is>
       </c>
       <c r="I17" s="1" t="n"/>
@@ -2657,12 +2653,12 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>maa://23890 (80.91), *maa://24940 (67.86)</t>
+          <t>maa://23890 (81.08), *maa://24940 (67.86), maa://56238 (100.0)</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n"/>
@@ -2726,7 +2722,7 @@
       </c>
       <c r="AF17" s="2" t="inlineStr">
         <is>
-          <t>maa://50136 (94.74)</t>
+          <t>maa://50136 (95.24)</t>
         </is>
       </c>
       <c r="AG17" s="1" t="n"/>
@@ -2744,7 +2740,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>maa://24570 (97.01)</t>
+          <t>maa://24570 (97.04)</t>
         </is>
       </c>
       <c r="E18" s="1" t="n"/>
@@ -2760,7 +2756,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>maa://24421 (87.46)</t>
+          <t>maa://24421 (87.14)</t>
         </is>
       </c>
       <c r="I18" s="1" t="n"/>
@@ -2776,7 +2772,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>maa://22466 (92.12), *maa://22732 (51.38), maa://52226 (94.74)</t>
+          <t>maa://22466 (92.12), *maa://22732 (51.38), maa://52226 (95.24)</t>
         </is>
       </c>
       <c r="M18" s="1" t="n"/>
@@ -2824,7 +2820,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>maa://21917 (97.09), maa://22741 (87.5)</t>
+          <t>maa://21917 (97.12), maa://22741 (87.5)</t>
         </is>
       </c>
       <c r="Y18" s="1" t="n"/>
@@ -2840,7 +2836,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>maa://24393 (98.15)</t>
+          <t>maa://24393 (98.18)</t>
         </is>
       </c>
       <c r="AC18" s="1" t="n"/>
@@ -2949,12 +2945,12 @@
       </c>
       <c r="W19" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>maa://31386 (100.0)</t>
+          <t>maa://31386 (100.0), maa://58490 (100.0)</t>
         </is>
       </c>
       <c r="Y19" s="1" t="n"/>
@@ -2970,7 +2966,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>*maa://30709 (68.07), *maa://36668 (57.32)</t>
+          <t>*maa://30709 (68.2), *maa://36668 (57.32)</t>
         </is>
       </c>
       <c r="AC19" s="1" t="n"/>
@@ -2986,7 +2982,7 @@
       </c>
       <c r="AF19" s="2" t="inlineStr">
         <is>
-          <t>*maa://21663 (63.64)</t>
+          <t>*maa://21663 (64.1)</t>
         </is>
       </c>
       <c r="AG19" s="1" t="n"/>
@@ -3004,7 +3000,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>maa://21432 (91.09), maa://25198 (94.57), *maa://20795 (50.76), maa://36680 (91.18)</t>
+          <t>maa://21432 (91.13), maa://25198 (94.62), *maa://20795 (50.76), maa://36680 (91.18)</t>
         </is>
       </c>
       <c r="E20" s="1" t="n"/>
@@ -3020,7 +3016,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>maa://22864 (90.71), ***maa://43283 (25.0), *maa://53361 (75.0)</t>
+          <t>maa://22864 (90.71), ***maa://43283 (25.0), **maa://53361 (42.86)</t>
         </is>
       </c>
       <c r="I20" s="1" t="n"/>
@@ -3036,7 +3032,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>maa://41331 (86.09)</t>
+          <t>maa://41331 (86.5)</t>
         </is>
       </c>
       <c r="M20" s="1" t="n"/>
@@ -3084,7 +3080,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>maa://50085 (86.96), maa://49976 (86.42), maa://56241 (100.0)</t>
+          <t>maa://50085 (87.39), maa://49976 (86.42), maa://56241 (100.0)</t>
         </is>
       </c>
       <c r="Y20" s="1" t="n"/>
@@ -3134,7 +3130,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>maa://21261 (97.96)</t>
+          <t>maa://21261 (98.0)</t>
         </is>
       </c>
       <c r="E21" s="1" t="n"/>
@@ -3166,7 +3162,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>maa://31731 (96.55)</t>
+          <t>maa://31731 (96.61)</t>
         </is>
       </c>
       <c r="M21" s="1" t="n"/>
@@ -3214,7 +3210,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>maa://20110 (86.76), maa://34946 (93.33)</t>
+          <t>maa://20110 (87.14), maa://34946 (93.33)</t>
         </is>
       </c>
       <c r="Y21" s="1" t="n"/>
@@ -3230,7 +3226,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>maa://21443 (82.64), ***maa://23820 (30.0), **maa://52223 (45.0)</t>
+          <t>maa://21443 (82.64), ***maa://23820 (30.0), **maa://52223 (39.13)</t>
         </is>
       </c>
       <c r="AC21" s="1" t="n"/>
@@ -3246,7 +3242,7 @@
       </c>
       <c r="AF21" s="2" t="inlineStr">
         <is>
-          <t>maa://22524 (89.47), maa://22432 (81.97)</t>
+          <t>maa://22524 (89.11), maa://22432 (82.54)</t>
         </is>
       </c>
       <c r="AG21" s="1" t="n"/>
@@ -3296,7 +3292,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>*maa://27127 (78.46), *maa://22751 (71.23)</t>
+          <t>*maa://27127 (78.63), *maa://22751 (71.23)</t>
         </is>
       </c>
       <c r="M22" s="1" t="n"/>
@@ -3328,7 +3324,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>maa://38495 (87.5)</t>
+          <t>maa://38495 (88.24)</t>
         </is>
       </c>
       <c r="U22" s="1" t="n"/>
@@ -3344,7 +3340,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>maa://21282 (98.71), *maa://37649 (72.5)</t>
+          <t>maa://21282 (98.72), *maa://37649 (73.17)</t>
         </is>
       </c>
       <c r="Y22" s="1" t="n"/>
@@ -3426,7 +3422,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>maa://39756 (95.59), maa://39875 (94.67)</t>
+          <t>maa://39756 (95.64), maa://39875 (94.81)</t>
         </is>
       </c>
       <c r="M23" s="1" t="n"/>
@@ -3442,7 +3438,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>maa://30587 (91.98), *maa://29748 (76.3), ***maa://29785 (17.39), *maa://37566 (78.26)</t>
+          <t>maa://30587 (92.02), *maa://29748 (76.3), ***maa://29785 (17.14), *maa://37566 (78.26)</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n"/>
@@ -3524,7 +3520,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>*maa://24368 (79.06), *maa://46650 (62.07)</t>
+          <t>*maa://24368 (79.22), *maa://46650 (62.07)</t>
         </is>
       </c>
       <c r="E24" s="1" t="n"/>
@@ -3604,7 +3600,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>maa://29988 (84.69), maa://23504 (93.6), **maa://22892 (41.29), *maa://25141 (77.37), *maa://36663 (78.0), ***maa://22815 (23.08), maa://52227 (100.0)</t>
+          <t>maa://29988 (84.8), maa://23504 (93.6), **maa://22892 (41.29), *maa://25141 (77.37), *maa://36663 (78.0), ***maa://22815 (23.08), maa://52227 (100.0)</t>
         </is>
       </c>
       <c r="Y24" s="1" t="n"/>
@@ -3636,7 +3632,7 @@
       </c>
       <c r="AF24" s="2" t="inlineStr">
         <is>
-          <t>maa://22523 (82.03), *maa://36672 (75.38), maa://29910 (93.75), **maa://21440 (35.71), maa://45831 (84.62)</t>
+          <t>maa://22523 (81.65), *maa://36672 (75.38), maa://29910 (93.75), **maa://21440 (35.71), maa://45831 (85.71)</t>
         </is>
       </c>
       <c r="AG24" s="1" t="n"/>
@@ -3654,7 +3650,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>maa://29753 (95.33)</t>
+          <t>maa://29753 (95.39)</t>
         </is>
       </c>
       <c r="E25" s="1" t="n"/>
@@ -3670,7 +3666,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>*maa://29063 (73.26), *maa://25311 (74.11), ***maa://22725 (4.76), *maa://45047 (66.67)</t>
+          <t>*maa://29063 (73.4), *maa://25311 (74.11), ***maa://22725 (4.76), *maa://45047 (66.67)</t>
         </is>
       </c>
       <c r="I25" s="1" t="n"/>
@@ -3686,7 +3682,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>maa://24378 (88.89)</t>
+          <t>maa://24378 (89.36)</t>
         </is>
       </c>
       <c r="M25" s="1" t="n"/>
@@ -3750,7 +3746,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>maa://31215 (89.13), *maa://24516 (79.35), maa://26001 (84.48)</t>
+          <t>maa://31215 (89.36), *maa://24516 (79.57), maa://26001 (84.75)</t>
         </is>
       </c>
       <c r="AC25" s="1" t="n"/>
@@ -3766,7 +3762,7 @@
       </c>
       <c r="AF25" s="2" t="inlineStr">
         <is>
-          <t>maa://20108 (95.86), maa://24621 (97.14), maa://36676 (97.06), maa://22771 (85.71), *maa://37772 (75.0)</t>
+          <t>maa://20108 (95.89), maa://24621 (97.14), maa://36676 (97.06), maa://22771 (85.71), *maa://37772 (75.0)</t>
         </is>
       </c>
       <c r="AG25" s="1" t="n"/>
@@ -3779,12 +3775,12 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>maa://41802 (93.1)</t>
+          <t>maa://41802 (93.1), maa://56374 (100.0)</t>
         </is>
       </c>
       <c r="E26" s="1" t="n"/>
@@ -3800,7 +3796,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>maa://24913 (92.0)</t>
+          <t>maa://24913 (92.08)</t>
         </is>
       </c>
       <c r="I26" s="1" t="n"/>
@@ -3827,12 +3823,12 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>*maa://30968 (65.0), maa://39870 (92.86)</t>
+          <t>*maa://30968 (65.0), maa://39870 (92.86), maa://56625 (100.0)</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n"/>
@@ -3864,7 +3860,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>maa://24389 (96.77)</t>
+          <t>maa://24389 (96.88)</t>
         </is>
       </c>
       <c r="Y26" s="1" t="n"/>
@@ -3880,7 +3876,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>maa://42235 (95.74)</t>
+          <t>maa://42235 (95.83)</t>
         </is>
       </c>
       <c r="AC26" s="1" t="n"/>
@@ -3896,7 +3892,7 @@
       </c>
       <c r="AF26" s="2" t="inlineStr">
         <is>
-          <t>*maa://30511 (77.08), *maa://29760 (56.25)</t>
+          <t>*maa://30511 (75.51), *maa://29760 (56.25)</t>
         </is>
       </c>
       <c r="AG26" s="1" t="n"/>
@@ -3930,7 +3926,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>*maa://39601 (79.17), **maa://21283 (47.37), maa://34494 (97.22), **maa://36665 (50.0)</t>
+          <t>*maa://39601 (79.17), **maa://21283 (48.05), maa://34494 (97.22), *maa://36665 (54.55)</t>
         </is>
       </c>
       <c r="I27" s="1" t="n"/>
@@ -3978,7 +3974,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>*maa://30624 (76.06)</t>
+          <t>*maa://30624 (76.39)</t>
         </is>
       </c>
       <c r="U27" s="1" t="n"/>
@@ -4044,7 +4040,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>maa://24465 (90.67), maa://25725 (84.38)</t>
+          <t>maa://24465 (90.59), maa://25725 (83.51)</t>
         </is>
       </c>
       <c r="E28" s="1" t="n"/>
@@ -4108,7 +4104,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>*maa://29765 (66.32), maa://23263 (95.41)</t>
+          <t>*maa://29765 (66.67), maa://23263 (95.45)</t>
         </is>
       </c>
       <c r="U28" s="1" t="n"/>
@@ -4124,7 +4120,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>maa://39929 (91.93), maa://41749 (91.85), ***maa://39723 (13.89)</t>
+          <t>maa://39929 (91.84), maa://41749 (91.97), ***maa://39723 (13.89)</t>
         </is>
       </c>
       <c r="Y28" s="1" t="n"/>
@@ -4156,7 +4152,7 @@
       </c>
       <c r="AF28" s="2" t="inlineStr">
         <is>
-          <t>maa://36660 (92.6), *maa://36701 (64.71)</t>
+          <t>maa://36660 (92.64), *maa://36701 (64.71)</t>
         </is>
       </c>
       <c r="AG28" s="1" t="n"/>
@@ -4190,7 +4186,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>*maa://25175 (58.46)</t>
+          <t>*maa://25175 (59.09)</t>
         </is>
       </c>
       <c r="I29" s="1" t="n"/>
@@ -4206,7 +4202,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>maa://28432 (94.01), maa://31400 (98.89), maa://28440 (83.7), *maa://28650 (71.43)</t>
+          <t>maa://28432 (94.01), maa://31400 (98.89), maa://28440 (83.94), *maa://28650 (71.43)</t>
         </is>
       </c>
       <c r="M29" s="1" t="n"/>
@@ -4400,7 +4396,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>maa://42979 (96.98), maa://45822 (100.0), maa://45045 (83.33)</t>
+          <t>maa://42979 (97.01), maa://45822 (100.0), maa://45045 (83.33)</t>
         </is>
       </c>
       <c r="AC30" s="1" t="n"/>
@@ -4466,7 +4462,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>maa://35926 (93.94), maa://36258 (87.26), *maa://43904 (71.43)</t>
+          <t>maa://35926 (93.67), maa://36258 (87.34), *maa://43904 (73.33)</t>
         </is>
       </c>
       <c r="M31" s="1" t="n"/>
@@ -4498,7 +4494,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>maa://30711 (96.83), maa://30768 (100.0)</t>
+          <t>maa://30711 (96.88), maa://30768 (100.0)</t>
         </is>
       </c>
       <c r="U31" s="1" t="n"/>
@@ -4530,7 +4526,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>***maa://51420 (20.0)</t>
+          <t>***maa://51420 (16.67)</t>
         </is>
       </c>
       <c r="AC31" s="1" t="n"/>
@@ -4580,7 +4576,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>maa://21895 (97.59), maa://36667 (97.17), **maa://20793 (38.0), maa://22760 (100.0)</t>
+          <t>maa://21895 (97.61), maa://36667 (97.17), **maa://20793 (38.0), maa://22760 (100.0)</t>
         </is>
       </c>
       <c r="I32" s="1" t="n"/>
@@ -4628,7 +4624,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>maa://42859 (97.34), maa://41108 (88.0), maa://41238 (97.96), maa://45523 (100.0)</t>
+          <t>maa://42859 (96.91), maa://41108 (86.27), maa://41238 (97.97), maa://45523 (100.0)</t>
         </is>
       </c>
       <c r="U32" s="1" t="n"/>
@@ -4867,12 +4863,12 @@
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>maa://48817 (96.43)</t>
+          <t>maa://48817 (96.55), maa://56235 (100.0)</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n"/>
@@ -4888,7 +4884,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>maa://24526 (92.28)</t>
+          <t>maa://24526 (92.31)</t>
         </is>
       </c>
       <c r="U34" s="1" t="n"/>
@@ -4986,7 +4982,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>maa://41296 (97.21)</t>
+          <t>maa://41296 (97.26)</t>
         </is>
       </c>
       <c r="M35" s="1" t="n"/>
@@ -5066,7 +5062,7 @@
       </c>
       <c r="AF35" s="2" t="inlineStr">
         <is>
-          <t>maa://39479 (91.3)</t>
+          <t>maa://39479 (91.67)</t>
         </is>
       </c>
       <c r="AG35" s="1" t="n"/>
@@ -5230,7 +5226,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>maa://45718 (98.38), maa://47069 (80.95), maa://45789 (100.0), maa://56336 (100.0)</t>
+          <t>maa://45718 (98.41), maa://47069 (81.82), maa://45789 (100.0), maa://56336 (100.0)</t>
         </is>
       </c>
       <c r="M37" s="1" t="n"/>
@@ -5363,7 +5359,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>maa://30713 (97.3)</t>
+          <t>maa://30713 (97.37)</t>
         </is>
       </c>
       <c r="U38" s="1" t="n"/>
@@ -5395,7 +5391,7 @@
       </c>
       <c r="AF38" s="2" t="inlineStr">
         <is>
-          <t>maa://36697 (89.19)</t>
+          <t>maa://36697 (89.33)</t>
         </is>
       </c>
       <c r="AG38" s="1" t="n"/>
@@ -5416,7 +5412,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>maa://36670 (89.19), maa://25199 (85.22), maa://30434 (92.68), maa://45059 (81.25), ***maa://25036 (18.52), *maa://44165 (66.67)</t>
+          <t>maa://36670 (89.19), maa://25199 (85.22), maa://30434 (92.86), maa://45059 (81.25), ***maa://25036 (18.52), *maa://44165 (66.67)</t>
         </is>
       </c>
       <c r="I39" s="1" t="n"/>
@@ -5448,7 +5444,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>maa://24709 (91.76), maa://47093 (100.0)</t>
+          <t>maa://24709 (91.81), maa://47093 (100.0)</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n"/>
@@ -5464,7 +5460,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>maa://47079 (95.65), *maa://45788 (74.36), maa://45790 (81.48)</t>
+          <t>maa://47079 (95.7), *maa://45788 (73.73), maa://45790 (81.48)</t>
         </is>
       </c>
       <c r="U39" s="1" t="n"/>
@@ -5549,7 +5545,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>maa://23278 (95.21), maa://21386 (95.79), maa://36664 (89.83), maa://45550 (87.5)</t>
+          <t>maa://23278 (95.22), maa://21386 (95.81), maa://36664 (89.83), maa://45550 (87.5)</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n"/>
@@ -5634,7 +5630,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>**maa://35616 (41.67), maa://43177 (90.62)</t>
+          <t>**maa://35616 (40.54), maa://43177 (87.88)</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n"/>
@@ -5772,7 +5768,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>maa://22525 (86.71), maa://21284 (87.04)</t>
+          <t>maa://22525 (86.16), maa://21284 (87.27)</t>
         </is>
       </c>
       <c r="I43" s="1" t="n"/>
@@ -5857,7 +5853,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>maa://29768 (98.26), maa://27728 (96.15)</t>
+          <t>maa://29768 (98.27), maa://27728 (96.19)</t>
         </is>
       </c>
       <c r="I44" s="1" t="n"/>
@@ -5926,7 +5922,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>maa://21229 (84.69), maa://30807 (94.67), *maa://22767 (54.55), maa://42459 (91.89), ***maa://20796 (13.79)</t>
+          <t>maa://21229 (84.26), maa://30807 (93.42), *maa://22767 (54.55), maa://42459 (89.47), ***maa://20796 (13.79)</t>
         </is>
       </c>
       <c r="I45" s="1" t="n"/>
@@ -5995,7 +5991,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>maa://35931 (92.49), maa://43901 (94.34)</t>
+          <t>maa://35931 (92.55), maa://43901 (94.34)</t>
         </is>
       </c>
       <c r="I46" s="1" t="n"/>
@@ -6043,12 +6039,12 @@
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>maa://27410 (96.84), maa://29661 (97.62), maa://28038 (84.62)</t>
+          <t>maa://27410 (96.87), maa://29661 (97.63), maa://28038 (84.62), maa://56236 (100.0)</t>
         </is>
       </c>
       <c r="I47" s="1" t="n"/>
@@ -6170,7 +6166,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>*maa://39643 (56.82)</t>
+          <t>*maa://39643 (57.78)</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n"/>
@@ -6357,7 +6353,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>maa://32534 (94.99), **maa://32434 (33.33)</t>
+          <t>maa://32534 (95.05), **maa://32434 (33.33)</t>
         </is>
       </c>
       <c r="I53" s="1" t="n"/>
@@ -6425,7 +6421,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>maa://32532 (93.09)</t>
+          <t>maa://32532 (93.19)</t>
         </is>
       </c>
       <c r="I55" s="1" t="n"/>
@@ -6461,7 +6457,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>maa://25176 (98.53), maa://56237 (100.0)</t>
+          <t>maa://25176 (98.57), maa://56237 (100.0)</t>
         </is>
       </c>
       <c r="I57" s="1" t="n"/>
@@ -6497,7 +6493,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>maa://31270 (94.52), maa://27746 (82.91)</t>
+          <t>maa://31270 (94.63), maa://27746 (82.91)</t>
         </is>
       </c>
       <c r="I59" s="1" t="n"/>
@@ -6515,7 +6511,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>*maa://40438 (73.33)</t>
+          <t>*maa://40438 (73.68)</t>
         </is>
       </c>
       <c r="I60" s="1" t="n"/>
@@ -6551,7 +6547,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>maa://42981 (96.55), maa://43903 (100.0), maa://56228 (100.0)</t>
+          <t>maa://42981 (96.61), maa://43903 (100.0), maa://56228 (100.0)</t>
         </is>
       </c>
       <c r="I62" s="1" t="n"/>

--- a/Excel/悖论模拟干员名单作者版.xlsx
+++ b/Excel/悖论模拟干员名单作者版.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>maa://25390 (95.33), maa://24702 (94.81), maa://36681 (86.42)</t>
+          <t>maa://25390 (95.45), maa://24702 (94.82), maa://36681 (86.42)</t>
         </is>
       </c>
       <c r="E2" s="1" t="n"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>maa://39402 (94.59), *maa://24633 (56.02), *maa://30515 (70.37), *maa://34787 (73.33), ***maa://20792 (11.93), ***maa://29083 (27.78), **maa://54304 (50.0)</t>
+          <t>maa://39402 (94.83), *maa://24633 (56.02), *maa://30515 (70.37), *maa://34787 (73.91), ***maa://20792 (11.93), ***maa://29083 (27.78), **maa://54304 (50.0)</t>
         </is>
       </c>
       <c r="M2" s="1" t="n"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>maa://22742 (91.04), *maa://20791 (62.65)</t>
+          <t>maa://22742 (91.39), *maa://20791 (62.65)</t>
         </is>
       </c>
       <c r="U2" s="1" t="n"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>maa://21246 (91.45), maa://36684 (93.59), ***maa://22731 (6.25)</t>
+          <t>maa://21246 (91.48), maa://36684 (93.12), ***maa://22731 (6.25)</t>
         </is>
       </c>
       <c r="AC2" s="1" t="n"/>
@@ -761,12 +761,12 @@
       </c>
       <c r="AE2" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>maa://25251 (91.79), **maa://21730 (31.76), ***maa://39501 (10.87), **maa://36675 (50.0)</t>
+          <t>maa://25251 (91.91), **maa://21730 (31.76), ***maa://39501 (10.64), **maa://36675 (50.0), maa://59087 (100.0)</t>
         </is>
       </c>
       <c r="AG2" s="1" t="n"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>maa://40192 (96.97), maa://36987 (96.15), maa://39849 (88.89)</t>
+          <t>maa://40192 (96.19), maa://36987 (96.15), maa://39849 (88.89)</t>
         </is>
       </c>
       <c r="E3" s="1" t="n"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>maa://21247 (98.42), *maa://22748 (60.0)</t>
+          <t>maa://21247 (98.43), *maa://22748 (60.0)</t>
         </is>
       </c>
       <c r="I3" s="1" t="n"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>*maa://22880 (65.79), maa://20276 (88.29), *maa://22749 (75.0)</t>
+          <t>*maa://22880 (65.8), maa://20276 (88.57), *maa://22749 (76.47)</t>
         </is>
       </c>
       <c r="M3" s="1" t="n"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>maa://21249 (94.62), maa://26254 (97.22), **maa://22738 (50.0)</t>
+          <t>maa://21249 (94.68), maa://26254 (97.22), *maa://22738 (66.67)</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>maa://24617 (90.84), maa://45854 (83.54), **maa://20790 (42.86), ***maa://37170 (16.44)</t>
+          <t>maa://24617 (90.91), maa://45854 (84.62), **maa://20790 (42.86), ***maa://37170 (16.44)</t>
         </is>
       </c>
       <c r="U3" s="1" t="n"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>maa://27396 (84.18), maa://27484 (96.27), maa://27480 (84.21)</t>
+          <t>maa://27396 (84.03), maa://27484 (96.32), maa://27480 (84.62)</t>
         </is>
       </c>
       <c r="Y3" s="1" t="n"/>
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>maa://24390 (95.51), maa://52241 (100.0)</t>
+          <t>maa://24390 (95.6), maa://52241 (100.0)</t>
         </is>
       </c>
       <c r="AC3" s="1" t="n"/>
@@ -896,7 +896,7 @@
       </c>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>*maa://21289 (75.76)</t>
+          <t>*maa://21289 (76.47)</t>
         </is>
       </c>
       <c r="AG3" s="1" t="n"/>
@@ -914,7 +914,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>maa://24632 (93.94), **maa://24303 (38.46), maa://22499 (86.67), maa://22746 (100.0)</t>
+          <t>maa://24632 (94.06), **maa://24303 (38.46), maa://22499 (86.67), maa://22746 (100.0)</t>
         </is>
       </c>
       <c r="E4" s="1" t="n"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>maa://49983 (95.38), maa://50121 (93.75)</t>
+          <t>maa://49983 (96.0), maa://50121 (94.74)</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>maa://32509 (94.66), maa://27295 (87.91), maa://22754 (89.19), *maa://31008 (79.55), *maa://21746 (54.55)</t>
+          <t>maa://32509 (93.98), maa://27295 (88.17), maa://22754 (89.19), *maa://31008 (79.55), *maa://21746 (54.55)</t>
         </is>
       </c>
       <c r="U4" s="1" t="n"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>**maa://32495 (48.76), maa://43217 (93.39), ***maa://31785 (22.22), ***maa://36683 (29.79)</t>
+          <t>**maa://32495 (48.76), maa://43217 (93.7), ***maa://31785 (22.22), ***maa://36683 (29.79)</t>
         </is>
       </c>
       <c r="Y4" s="1" t="n"/>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>*maa://32658 (76.0)</t>
+          <t>*maa://32658 (76.92)</t>
         </is>
       </c>
       <c r="AC4" s="1" t="n"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>maa://21245 (84.7), maa://22744 (81.48), maa://54105 (100.0)</t>
+          <t>maa://21245 (84.51), maa://22744 (82.14), maa://54105 (100.0)</t>
         </is>
       </c>
       <c r="E5" s="1" t="n"/>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>maa://21919 (97.01), *maa://21281 (80.0)</t>
+          <t>maa://21919 (97.06), *maa://21281 (80.0)</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n"/>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>maa://42407 (95.0)</t>
+          <t>maa://42407 (95.06)</t>
         </is>
       </c>
       <c r="E6" s="1" t="n"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>maa://24370 (96.88)</t>
+          <t>maa://24370 (96.92)</t>
         </is>
       </c>
       <c r="I6" s="1" t="n"/>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>maa://24839 (98.81)</t>
+          <t>maa://24839 (98.83)</t>
         </is>
       </c>
       <c r="M6" s="1" t="n"/>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>maa://52754 (88.89)</t>
+          <t>*maa://52754 (80.0)</t>
         </is>
       </c>
       <c r="Y6" s="1" t="n"/>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="AF6" s="2" t="inlineStr">
         <is>
-          <t>*maa://33152 (62.71), ***maa://22770 (26.09)</t>
+          <t>*maa://33152 (63.93), ***maa://22770 (26.09)</t>
         </is>
       </c>
       <c r="AG6" s="1" t="n"/>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>*maa://22763 (65.71)</t>
+          <t>*maa://22763 (66.67)</t>
         </is>
       </c>
       <c r="I7" s="1" t="n"/>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>maa://28624 (93.62), maa://24957 (97.78)</t>
+          <t>maa://28624 (93.71), maa://24957 (97.78)</t>
         </is>
       </c>
       <c r="M7" s="1" t="n"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>maa://22750 (92.73)</t>
+          <t>maa://22750 (92.98)</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n"/>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>maa://21291 (86.21)</t>
+          <t>maa://21291 (86.67)</t>
         </is>
       </c>
       <c r="U7" s="1" t="n"/>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>maa://22399 (96.13), *maa://22758 (77.22)</t>
+          <t>maa://22399 (96.2), *maa://22758 (77.22)</t>
         </is>
       </c>
       <c r="Y7" s="1" t="n"/>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AF7" s="2" t="inlineStr">
         <is>
-          <t>*maa://26191 (67.42), maa://45272 (96.88), *maa://36671 (69.23), *maa://42530 (62.5)</t>
+          <t>*maa://26191 (67.42), maa://45272 (96.97), *maa://36671 (69.23), *maa://42530 (62.5)</t>
         </is>
       </c>
       <c r="AG7" s="1" t="n"/>
@@ -1429,7 +1429,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>更新日期：2025.05.24 13:19:10</t>
+          <t>更新日期：2025.06.07 13:19:20</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>*maa://21476 (75.44), *maa://39431 (56.25), **maa://37551 (50.0)</t>
+          <t>*maa://21476 (76.27), *maa://39431 (58.82), **maa://37551 (50.0)</t>
         </is>
       </c>
       <c r="E8" s="1" t="n"/>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>maa://32931 (84.17), *maa://21916 (63.24), maa://23252 (91.55), maa://37496 (97.44), **maa://22759 (45.45)</t>
+          <t>maa://32931 (83.8), *maa://21916 (62.32), maa://23252 (91.67), maa://37496 (97.5), **maa://22759 (45.45)</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n"/>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>maa://21411 (95.96)</t>
+          <t>maa://21411 (96.06)</t>
         </is>
       </c>
       <c r="Y8" s="1" t="n"/>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>maa://25389 (90.24)</t>
+          <t>maa://25389 (90.48)</t>
         </is>
       </c>
       <c r="AC8" s="1" t="n"/>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AF8" s="2" t="inlineStr">
         <is>
-          <t>*maa://24479 (78.12), *maa://21990 (51.85)</t>
+          <t>*maa://24479 (77.32), *maa://21990 (51.85)</t>
         </is>
       </c>
       <c r="AG8" s="1" t="n"/>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>**maa://47450 (33.33)</t>
+          <t>**maa://47450 (40.0), maa://56348 (100.0)</t>
         </is>
       </c>
       <c r="I9" s="1" t="n"/>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>maa://22762 (92.78), maa://39552 (83.33)</t>
+          <t>maa://22762 (92.93), maa://39552 (83.33)</t>
         </is>
       </c>
       <c r="M9" s="1" t="n"/>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>maa://22736 (83.04)</t>
+          <t>maa://22736 (83.33)</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n"/>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>maa://26222 (98.31), **maa://22866 (30.19)</t>
+          <t>maa://26222 (98.33), **maa://22866 (30.19)</t>
         </is>
       </c>
       <c r="U9" s="1" t="n"/>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>maa://26223 (98.11), maa://52237 (100.0)</t>
+          <t>maa://26223 (98.14), maa://52237 (100.0)</t>
         </is>
       </c>
       <c r="Y9" s="1" t="n"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>maa://28711 (87.14), **maa://39938 (45.24), **maa://45044 (40.0), maa://40166 (94.74), **maa://27377 (42.86), ***maa://25174 (19.05)</t>
+          <t>maa://28711 (87.23), **maa://39938 (45.24), **maa://45044 (50.0), maa://40166 (93.75), **maa://27377 (42.86), ***maa://25174 (19.05)</t>
         </is>
       </c>
       <c r="AC9" s="1" t="n"/>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AF9" s="2" t="inlineStr">
         <is>
-          <t>maa://26206 (88.89), *maa://22865 (51.85)</t>
+          <t>maa://26206 (89.14), *maa://22865 (53.57)</t>
         </is>
       </c>
       <c r="AG9" s="1" t="n"/>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>***maa://25695 (18.81), ***maa://39951 (12.33), ***maa://34206 (22.22), *maa://45271 (60.0), ***maa://39243 (25.0), maa://54000 (100.0)</t>
+          <t>***maa://25695 (18.72), ***maa://39951 (12.0), ***maa://34206 (22.22), *maa://45271 (61.33), ***maa://39243 (25.0), **maa://54000 (50.0)</t>
         </is>
       </c>
       <c r="E10" s="1" t="n"/>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>**maa://24395 (38.89)</t>
+          <t>**maa://24395 (37.84)</t>
         </is>
       </c>
       <c r="M10" s="1" t="n"/>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>maa://28977 (88.42), maa://36669 (82.35), *maa://23264 (61.4)</t>
+          <t>maa://28977 (88.54), maa://36669 (83.02), *maa://23264 (61.4)</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n"/>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>maa://27395 (96.64), maa://22755 (88.89), **maa://22756 (40.91), ***maa://21737 (11.76)</t>
+          <t>maa://27395 (96.73), maa://22755 (89.06), **maa://22756 (40.91), ***maa://21737 (11.76)</t>
         </is>
       </c>
       <c r="U10" s="1" t="n"/>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>maa://22301 (97.89), maa://45828 (93.18), maa://22726 (100.0)</t>
+          <t>maa://22301 (97.9), maa://45828 (93.33), maa://22726 (100.0)</t>
         </is>
       </c>
       <c r="Y10" s="1" t="n"/>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AF10" s="2" t="inlineStr">
         <is>
-          <t>*maa://25021 (53.85), *maa://22733 (65.0), **maa://22761 (50.0)</t>
+          <t>*maa://25021 (53.77), *maa://22733 (64.29), **maa://22761 (50.0)</t>
         </is>
       </c>
       <c r="AG10" s="1" t="n"/>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>maa://36707 (99.37)</t>
+          <t>maa://36707 (99.39)</t>
         </is>
       </c>
       <c r="E11" s="1" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>maa://21287 (88.79)</t>
+          <t>maa://21287 (89.08)</t>
         </is>
       </c>
       <c r="M11" s="1" t="n"/>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>maa://22747 (90.8), maa://22501 (98.15), maa://45521 (91.43)</t>
+          <t>maa://22747 (90.96), maa://22501 (98.21), maa://45521 (91.43)</t>
         </is>
       </c>
       <c r="U11" s="1" t="n"/>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>maa://36713 (98.1)</t>
+          <t>maa://36713 (98.14)</t>
         </is>
       </c>
       <c r="Y11" s="1" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>maa://29912 (97.78), maa://22516 (87.36), *maa://20794 (55.84)</t>
+          <t>maa://29912 (97.78), maa://22516 (87.36), *maa://20794 (56.96)</t>
         </is>
       </c>
       <c r="AC11" s="1" t="n"/>
@@ -2007,12 +2007,12 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>maa://57541 (100.0)</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>maa://22753 (91.83), *maa://21485 (75.84), maa://37962 (91.8)</t>
+          <t>maa://22753 (91.9), *maa://21485 (75.84), maa://37962 (92.54)</t>
         </is>
       </c>
       <c r="Y12" s="1" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>maa://23669 (95.64), maa://36677 (95.18), maa://39872 (93.1)</t>
+          <t>maa://23669 (95.65), maa://36677 (95.35), maa://39872 (93.1)</t>
         </is>
       </c>
       <c r="AC12" s="1" t="n"/>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="AF12" s="2" t="inlineStr">
         <is>
-          <t>*maa://28932 (79.19), *maa://20106 (64.29), *maa://22769 (64.29)</t>
+          <t>*maa://28932 (78.98), *maa://20106 (64.29), *maa://22769 (64.29)</t>
         </is>
       </c>
       <c r="AG12" s="1" t="n"/>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>maa://24999 (92.7), maa://36673 (91.86), maa://25001 (86.49)</t>
+          <t>maa://24999 (92.81), maa://36673 (91.95), maa://25001 (86.49)</t>
         </is>
       </c>
       <c r="E13" s="1" t="n"/>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>*maa://21248 (73.45), **maa://22728 (45.65)</t>
+          <t>*maa://21248 (73.84), **maa://22728 (46.94)</t>
         </is>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>maa://22676 (93.57), *maa://22583 (77.22), *maa://22500 (59.57), maa://48321 (100.0)</t>
+          <t>maa://22676 (93.66), *maa://22583 (77.78), *maa://22500 (59.57), maa://48321 (91.67)</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>maa://34957 (83.02), **maa://22768 (50.0)</t>
+          <t>maa://34957 (83.78), **maa://22768 (50.0)</t>
         </is>
       </c>
       <c r="Y13" s="1" t="n"/>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AF13" s="2" t="inlineStr">
         <is>
-          <t>**maa://22737 (38.22), maa://39883 (87.6), **maa://39885 (50.0)</t>
+          <t>**maa://22737 (38.61), maa://39883 (87.2), **maa://39885 (50.0)</t>
         </is>
       </c>
       <c r="AG13" s="1" t="n"/>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>maa://30764 (89.71)</t>
+          <t>maa://30764 (89.86)</t>
         </is>
       </c>
       <c r="E14" s="1" t="n"/>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>maa://39841 (94.16), maa://26245 (96.59), maa://21288 (96.3), maa://36682 (95.83)</t>
+          <t>maa://39841 (94.27), maa://26245 (96.67), maa://21288 (96.3), maa://36682 (95.92)</t>
         </is>
       </c>
       <c r="M14" s="1" t="n"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>maa://23250 (98.84), maa://20107 (87.1), maa://22772 (100.0), *maa://22745 (66.67)</t>
+          <t>maa://23250 (98.86), maa://20107 (87.1), maa://22772 (100.0), *maa://22745 (66.67)</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n"/>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>maa://37468 (91.67)</t>
+          <t>maa://37468 (92.0)</t>
         </is>
       </c>
       <c r="Y14" s="1" t="n"/>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>maa://22764 (96.39)</t>
+          <t>maa://22764 (96.43)</t>
         </is>
       </c>
       <c r="AC14" s="1" t="n"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>*maa://22743 (79.08), maa://22734 (84.55), *maa://30808 (65.71), *maa://36048 (67.31), maa://45058 (84.21)</t>
+          <t>*maa://22743 (78.84), maa://22734 (84.55), *maa://30808 (65.71), *maa://36048 (69.09), maa://45058 (84.21)</t>
         </is>
       </c>
       <c r="E15" s="1" t="n"/>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>maa://24304 (87.1), maa://21478 (90.0)</t>
+          <t>maa://24304 (87.01), maa://21478 (90.0)</t>
         </is>
       </c>
       <c r="I15" s="1" t="n"/>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>maa://24762 (91.21), *maa://22727 (70.0)</t>
+          <t>maa://24762 (91.35), *maa://22727 (70.0)</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n"/>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>maa://23892 (96.55)</t>
+          <t>maa://23892 (96.59)</t>
         </is>
       </c>
       <c r="U15" s="1" t="n"/>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AF15" s="2" t="inlineStr">
         <is>
-          <t>maa://21364 (81.1), maa://36666 (81.46), *maa://22766 (68.29)</t>
+          <t>maa://21364 (81.2), maa://36666 (82.39), *maa://22766 (68.55)</t>
         </is>
       </c>
       <c r="AG15" s="1" t="n"/>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>maa://21441 (96.54), maa://37650 (96.3), maa://36679 (94.55)</t>
+          <t>maa://21441 (96.54), maa://37650 (96.43), maa://36679 (94.55)</t>
         </is>
       </c>
       <c r="E16" s="1" t="n"/>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>maa://28504 (92.54)</t>
+          <t>maa://28504 (92.65)</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>maa://22729 (94.44), *maa://28648 (73.75), *maa://36674 (80.0)</t>
+          <t>maa://22729 (94.48), *maa://28648 (73.75), *maa://36674 (80.0)</t>
         </is>
       </c>
       <c r="U16" s="1" t="n"/>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>maa://28501 (98.26), maa://28051 (96.0)</t>
+          <t>maa://28501 (98.28), maa://28051 (96.0)</t>
         </is>
       </c>
       <c r="Y16" s="1" t="n"/>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>maa://26228 (95.45)</t>
+          <t>maa://26228 (95.61)</t>
         </is>
       </c>
       <c r="AC16" s="1" t="n"/>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="AF16" s="2" t="inlineStr">
         <is>
-          <t>*maa://23911 (69.17), maa://27755 (94.06)</t>
+          <t>*maa://23911 (69.42), maa://27755 (94.06)</t>
         </is>
       </c>
       <c r="AG16" s="1" t="n"/>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>maa://22430 (89.52), maa://39599 (85.53)</t>
+          <t>maa://22430 (89.67), maa://39599 (86.25)</t>
         </is>
       </c>
       <c r="I17" s="1" t="n"/>
@@ -2657,12 +2657,12 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>maa://23890 (80.91), *maa://24940 (67.86)</t>
+          <t>maa://23890 (81.08), *maa://24940 (67.86), maa://56238 (100.0)</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n"/>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AF17" s="2" t="inlineStr">
         <is>
-          <t>maa://50136 (94.74)</t>
+          <t>maa://50136 (95.45)</t>
         </is>
       </c>
       <c r="AG17" s="1" t="n"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>maa://24570 (97.01)</t>
+          <t>maa://24570 (97.06)</t>
         </is>
       </c>
       <c r="E18" s="1" t="n"/>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>maa://24421 (87.46)</t>
+          <t>maa://24421 (87.19)</t>
         </is>
       </c>
       <c r="I18" s="1" t="n"/>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>maa://22466 (92.12), *maa://22732 (51.38), maa://52226 (94.74)</t>
+          <t>maa://22466 (92.12), *maa://22732 (51.38), maa://52226 (95.45)</t>
         </is>
       </c>
       <c r="M18" s="1" t="n"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>maa://21917 (97.09), maa://22741 (87.5)</t>
+          <t>maa://21917 (97.12), maa://22741 (87.5)</t>
         </is>
       </c>
       <c r="Y18" s="1" t="n"/>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>maa://24393 (98.15)</t>
+          <t>maa://24393 (98.18)</t>
         </is>
       </c>
       <c r="AC18" s="1" t="n"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>maa://24386 (98.64)</t>
+          <t>maa://24386 (98.65)</t>
         </is>
       </c>
       <c r="U19" s="1" t="n"/>
@@ -2949,12 +2949,12 @@
       </c>
       <c r="W19" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>maa://31386 (100.0)</t>
+          <t>maa://31386 (100.0), maa://58490 (100.0)</t>
         </is>
       </c>
       <c r="Y19" s="1" t="n"/>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>*maa://30709 (68.07), *maa://36668 (57.32)</t>
+          <t>*maa://30709 (68.4), *maa://36668 (57.32)</t>
         </is>
       </c>
       <c r="AC19" s="1" t="n"/>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AF19" s="2" t="inlineStr">
         <is>
-          <t>*maa://21663 (63.64)</t>
+          <t>*maa://21663 (64.1)</t>
         </is>
       </c>
       <c r="AG19" s="1" t="n"/>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>maa://21432 (91.09), maa://25198 (94.57), *maa://20795 (50.76), maa://36680 (91.18)</t>
+          <t>maa://21432 (90.73), maa://25198 (93.89), *maa://20795 (50.76), maa://36680 (91.18)</t>
         </is>
       </c>
       <c r="E20" s="1" t="n"/>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>maa://22864 (90.71), ***maa://43283 (25.0), *maa://53361 (75.0)</t>
+          <t>maa://22864 (90.81), **maa://53361 (42.86), ***maa://43283 (25.0)</t>
         </is>
       </c>
       <c r="I20" s="1" t="n"/>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>maa://41331 (86.09)</t>
+          <t>maa://41331 (86.94)</t>
         </is>
       </c>
       <c r="M20" s="1" t="n"/>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>maa://37442 (96.0)</t>
+          <t>maa://37442 (96.15)</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n"/>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>maa://50085 (86.96), maa://49976 (86.42), maa://56241 (100.0)</t>
+          <t>maa://50085 (87.79), maa://49976 (86.59), maa://56241 (100.0)</t>
         </is>
       </c>
       <c r="Y20" s="1" t="n"/>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>maa://21261 (97.96)</t>
+          <t>maa://21261 (98.0)</t>
         </is>
       </c>
       <c r="E21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>maa://31731 (96.55)</t>
+          <t>maa://31731 (96.72)</t>
         </is>
       </c>
       <c r="M21" s="1" t="n"/>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>maa://20110 (86.76), maa://34946 (93.33)</t>
+          <t>maa://20110 (87.14), maa://34946 (93.33)</t>
         </is>
       </c>
       <c r="Y21" s="1" t="n"/>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>maa://21443 (82.64), ***maa://23820 (30.0), **maa://52223 (45.0)</t>
+          <t>maa://21443 (82.73), ***maa://23820 (30.0), **maa://52223 (41.38)</t>
         </is>
       </c>
       <c r="AC21" s="1" t="n"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="AF21" s="2" t="inlineStr">
         <is>
-          <t>maa://22524 (89.47), maa://22432 (81.97)</t>
+          <t>maa://22524 (89.11), maa://22432 (83.08)</t>
         </is>
       </c>
       <c r="AG21" s="1" t="n"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>*maa://27127 (78.46), *maa://22751 (71.23)</t>
+          <t>*maa://27127 (78.2), *maa://22751 (70.27)</t>
         </is>
       </c>
       <c r="M22" s="1" t="n"/>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>maa://38495 (87.5)</t>
+          <t>maa://38495 (88.24)</t>
         </is>
       </c>
       <c r="U22" s="1" t="n"/>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>maa://21282 (98.71), *maa://37649 (72.5)</t>
+          <t>maa://21282 (98.72), *maa://37649 (73.17)</t>
         </is>
       </c>
       <c r="Y22" s="1" t="n"/>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>***maa://28036 (27.85), **maa://41753 (50.0)</t>
+          <t>***maa://28036 (28.75), *maa://41753 (51.85)</t>
         </is>
       </c>
       <c r="E23" s="1" t="n"/>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>maa://39756 (95.59), maa://39875 (94.67)</t>
+          <t>maa://39756 (95.74), maa://39875 (94.81)</t>
         </is>
       </c>
       <c r="M23" s="1" t="n"/>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>maa://30587 (91.98), *maa://29748 (76.3), ***maa://29785 (17.39), *maa://37566 (78.26)</t>
+          <t>maa://30587 (92.06), *maa://29748 (76.3), ***maa://29785 (17.14), *maa://37566 (78.26)</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n"/>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>*maa://24368 (79.06), *maa://46650 (62.07)</t>
+          <t>*maa://24368 (79.13), *maa://46650 (62.07)</t>
         </is>
       </c>
       <c r="E24" s="1" t="n"/>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>maa://29988 (84.69), maa://23504 (93.6), **maa://22892 (41.29), *maa://25141 (77.37), *maa://36663 (78.0), ***maa://22815 (23.08), maa://52227 (100.0)</t>
+          <t>maa://29988 (84.9), maa://23504 (93.66), **maa://22892 (41.29), *maa://25141 (77.37), *maa://36663 (78.0), ***maa://22815 (23.08), maa://52227 (100.0)</t>
         </is>
       </c>
       <c r="Y24" s="1" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>maa://39349 (85.71)</t>
+          <t>maa://39349 (87.5)</t>
         </is>
       </c>
       <c r="AC24" s="1" t="n"/>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="AF24" s="2" t="inlineStr">
         <is>
-          <t>maa://22523 (82.03), *maa://36672 (75.38), maa://29910 (93.75), **maa://21440 (35.71), maa://45831 (84.62)</t>
+          <t>maa://22523 (81.74), *maa://36672 (75.38), maa://29910 (93.75), **maa://21440 (35.71), maa://45831 (85.71)</t>
         </is>
       </c>
       <c r="AG24" s="1" t="n"/>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>maa://29753 (95.33)</t>
+          <t>maa://29753 (95.42)</t>
         </is>
       </c>
       <c r="E25" s="1" t="n"/>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>*maa://29063 (73.26), *maa://25311 (74.11), ***maa://22725 (4.76), *maa://45047 (66.67)</t>
+          <t>*maa://29063 (72.54), *maa://25311 (74.11), ***maa://22725 (4.76), *maa://45047 (71.43)</t>
         </is>
       </c>
       <c r="I25" s="1" t="n"/>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>maa://24378 (88.89)</t>
+          <t>maa://24378 (89.8)</t>
         </is>
       </c>
       <c r="M25" s="1" t="n"/>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>maa://29890 (83.05)</t>
+          <t>maa://29890 (83.33)</t>
         </is>
       </c>
       <c r="Y25" s="1" t="n"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>maa://31215 (89.13), *maa://24516 (79.35), maa://26001 (84.48)</t>
+          <t>maa://31215 (89.44), *maa://24516 (79.57), maa://26001 (84.75)</t>
         </is>
       </c>
       <c r="AC25" s="1" t="n"/>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="AF25" s="2" t="inlineStr">
         <is>
-          <t>maa://20108 (95.86), maa://24621 (97.14), maa://36676 (97.06), maa://22771 (85.71), *maa://37772 (75.0)</t>
+          <t>maa://20108 (95.89), maa://24621 (97.14), maa://36676 (97.06), maa://22771 (85.71), *maa://37772 (75.0)</t>
         </is>
       </c>
       <c r="AG25" s="1" t="n"/>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>maa://41802 (93.1)</t>
+          <t>maa://41802 (93.33), maa://56374 (100.0)</t>
         </is>
       </c>
       <c r="E26" s="1" t="n"/>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>maa://24913 (92.0)</t>
+          <t>maa://24913 (91.26), **maa://56240 (50.0)</t>
         </is>
       </c>
       <c r="I26" s="1" t="n"/>
@@ -3827,12 +3827,12 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>*maa://30968 (65.0), maa://39870 (92.86)</t>
+          <t>*maa://30968 (65.0), maa://39870 (92.86), maa://56625 (100.0)</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n"/>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>maa://24389 (96.77)</t>
+          <t>maa://24389 (96.88)</t>
         </is>
       </c>
       <c r="Y26" s="1" t="n"/>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>maa://42235 (95.74)</t>
+          <t>maa://42235 (95.95)</t>
         </is>
       </c>
       <c r="AC26" s="1" t="n"/>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="AF26" s="2" t="inlineStr">
         <is>
-          <t>*maa://30511 (77.08), *maa://29760 (56.25)</t>
+          <t>*maa://30511 (75.0), *maa://29760 (52.94)</t>
         </is>
       </c>
       <c r="AG26" s="1" t="n"/>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>*maa://39601 (79.17), **maa://21283 (47.37), maa://34494 (97.22), **maa://36665 (50.0)</t>
+          <t>*maa://39601 (79.17), **maa://21283 (48.05), maa://34494 (97.22), *maa://36665 (54.55)</t>
         </is>
       </c>
       <c r="I27" s="1" t="n"/>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>*maa://30624 (76.06)</t>
+          <t>*maa://30624 (77.03)</t>
         </is>
       </c>
       <c r="U27" s="1" t="n"/>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>maa://24465 (90.67), maa://25725 (84.38)</t>
+          <t>maa://24465 (90.62), maa://25725 (82.83)</t>
         </is>
       </c>
       <c r="E28" s="1" t="n"/>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>*maa://29765 (66.32), maa://23263 (95.41)</t>
+          <t>*maa://29765 (66.67), maa://23263 (95.45)</t>
         </is>
       </c>
       <c r="U28" s="1" t="n"/>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>maa://39929 (91.93), maa://41749 (91.85), ***maa://39723 (13.89)</t>
+          <t>maa://39929 (91.9), maa://41749 (92.25), ***maa://39723 (13.89)</t>
         </is>
       </c>
       <c r="Y28" s="1" t="n"/>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AF28" s="2" t="inlineStr">
         <is>
-          <t>maa://36660 (92.6), *maa://36701 (64.71)</t>
+          <t>maa://36660 (92.51), *maa://36701 (64.71)</t>
         </is>
       </c>
       <c r="AG28" s="1" t="n"/>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>maa://31694 (98.31)</t>
+          <t>maa://31694 (98.33)</t>
         </is>
       </c>
       <c r="E29" s="1" t="n"/>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>*maa://25175 (58.46)</t>
+          <t>*maa://25175 (59.09)</t>
         </is>
       </c>
       <c r="I29" s="1" t="n"/>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>maa://28432 (94.01), maa://31400 (98.89), maa://28440 (83.7), *maa://28650 (71.43)</t>
+          <t>maa://28432 (94.02), maa://31400 (98.89), maa://28440 (83.94), *maa://28650 (71.43)</t>
         </is>
       </c>
       <c r="M29" s="1" t="n"/>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>*maa://23168 (56.72), *maa://30050 (51.22), maa://54169 (100.0)</t>
+          <t>*maa://23168 (56.72), *maa://30050 (52.38), maa://54169 (100.0)</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n"/>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AF29" s="2" t="inlineStr">
         <is>
-          <t>*maa://24080 (69.17), maa://42865 (80.19), ***maa://34960 (8.33)</t>
+          <t>*maa://24080 (69.17), *maa://42865 (80.0), ***maa://34960 (8.33)</t>
         </is>
       </c>
       <c r="AG29" s="1" t="n"/>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>maa://45792 (89.29)</t>
+          <t>maa://45792 (89.66)</t>
         </is>
       </c>
       <c r="E30" s="1" t="n"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>maa://21442 (98.78)</t>
+          <t>maa://21442 (98.79)</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n"/>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>maa://42979 (96.98), maa://45822 (100.0), maa://45045 (83.33)</t>
+          <t>maa://42979 (97.06), maa://45822 (100.0), maa://45045 (83.33)</t>
         </is>
       </c>
       <c r="AC30" s="1" t="n"/>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>maa://35926 (93.94), maa://36258 (87.26), *maa://43904 (71.43)</t>
+          <t>maa://35926 (93.69), maa://36258 (87.65), *maa://43904 (73.33)</t>
         </is>
       </c>
       <c r="M31" s="1" t="n"/>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>maa://30711 (96.83), maa://30768 (100.0)</t>
+          <t>maa://30711 (96.92), maa://30768 (100.0)</t>
         </is>
       </c>
       <c r="U31" s="1" t="n"/>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>***maa://51420 (20.0)</t>
+          <t>***maa://51420 (16.67)</t>
         </is>
       </c>
       <c r="AC31" s="1" t="n"/>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>maa://21895 (97.59), maa://36667 (97.17), **maa://20793 (38.0), maa://22760 (100.0)</t>
+          <t>maa://21895 (97.62), maa://36667 (97.25), **maa://20793 (39.22), maa://22760 (100.0)</t>
         </is>
       </c>
       <c r="I32" s="1" t="n"/>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>maa://42859 (97.34), maa://41108 (88.0), maa://41238 (97.96), maa://45523 (100.0)</t>
+          <t>maa://42859 (96.95), maa://41108 (86.27), maa://41238 (97.99), maa://45523 (100.0)</t>
         </is>
       </c>
       <c r="U32" s="1" t="n"/>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="AF32" s="2" t="inlineStr">
         <is>
-          <t>maa://42408 (87.5)</t>
+          <t>maa://42408 (88.24)</t>
         </is>
       </c>
       <c r="AG32" s="1" t="n"/>
@@ -4867,12 +4867,12 @@
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>maa://48817 (96.43)</t>
+          <t>maa://48817 (96.72), maa://56235 (100.0)</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n"/>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>maa://24526 (92.28)</t>
+          <t>maa://24526 (92.31)</t>
         </is>
       </c>
       <c r="U34" s="1" t="n"/>
@@ -4915,12 +4915,12 @@
       </c>
       <c r="AA34" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AC34" s="1" t="n"/>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="AF34" s="2" t="inlineStr">
         <is>
-          <t>*maa://32650 (80.0)</t>
+          <t>maa://32650 (80.77)</t>
         </is>
       </c>
       <c r="AG34" s="1" t="n"/>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>maa://41296 (97.21)</t>
+          <t>maa://41296 (97.3)</t>
         </is>
       </c>
       <c r="M35" s="1" t="n"/>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AF35" s="2" t="inlineStr">
         <is>
-          <t>maa://39479 (91.3)</t>
+          <t>maa://39479 (91.67)</t>
         </is>
       </c>
       <c r="AG35" s="1" t="n"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>maa://24375 (90.48)</t>
+          <t>maa://24375 (90.7)</t>
         </is>
       </c>
       <c r="I36" s="1" t="n"/>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>maa://27613 (99.11)</t>
+          <t>maa://27613 (99.12)</t>
         </is>
       </c>
       <c r="U36" s="1" t="n"/>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>maa://45718 (98.38), maa://47069 (80.95), maa://45789 (100.0), maa://56336 (100.0)</t>
+          <t>maa://45718 (98.43), maa://47069 (81.82), maa://56336 (85.71), maa://45789 (100.0)</t>
         </is>
       </c>
       <c r="M37" s="1" t="n"/>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>maa://21280 (90.0), *maa://21239 (71.43)</t>
+          <t>maa://21280 (89.61), *maa://21239 (71.43)</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>maa://30713 (97.3)</t>
+          <t>maa://30713 (97.37)</t>
         </is>
       </c>
       <c r="U38" s="1" t="n"/>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="AF38" s="2" t="inlineStr">
         <is>
-          <t>maa://36697 (89.19)</t>
+          <t>maa://36697 (89.22)</t>
         </is>
       </c>
       <c r="AG38" s="1" t="n"/>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>maa://36670 (89.19), maa://25199 (85.22), maa://30434 (92.68), maa://45059 (81.25), ***maa://25036 (18.52), *maa://44165 (66.67)</t>
+          <t>maa://36670 (89.38), maa://25199 (85.22), maa://30434 (93.02), *maa://45059 (78.79), ***maa://25036 (18.52), *maa://44165 (66.67)</t>
         </is>
       </c>
       <c r="I39" s="1" t="n"/>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>maa://24709 (91.76), maa://47093 (100.0)</t>
+          <t>maa://24709 (91.91), maa://47093 (100.0)</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n"/>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>maa://47079 (95.65), *maa://45788 (74.36), maa://45790 (81.48)</t>
+          <t>maa://47079 (95.83), *maa://45788 (73.73), maa://45790 (82.76)</t>
         </is>
       </c>
       <c r="U39" s="1" t="n"/>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>maa://23278 (95.21), maa://21386 (95.79), maa://36664 (89.83), maa://45550 (87.5)</t>
+          <t>maa://23278 (95.24), maa://21386 (95.81), maa://36664 (90.0), maa://45550 (87.5)</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n"/>
@@ -5569,6 +5569,22 @@
         </is>
       </c>
       <c r="U40" s="1" t="n"/>
+      <c r="Z40" s="1" t="inlineStr">
+        <is>
+          <t>酒神</t>
+        </is>
+      </c>
+      <c r="AA40" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB40" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC40" s="1" t="n"/>
       <c r="AD40" s="1" t="inlineStr">
         <is>
           <t>云迹</t>
@@ -5634,7 +5650,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>**maa://35616 (41.67), maa://43177 (90.62)</t>
+          <t>**maa://35616 (40.54), maa://43177 (87.88)</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n"/>
@@ -5772,7 +5788,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>maa://22525 (86.71), maa://21284 (87.04)</t>
+          <t>maa://22525 (84.66), maa://21284 (87.27)</t>
         </is>
       </c>
       <c r="I43" s="1" t="n"/>
@@ -5857,7 +5873,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>maa://29768 (98.26), maa://27728 (96.15)</t>
+          <t>maa://29768 (97.94), maa://27728 (96.19)</t>
         </is>
       </c>
       <c r="I44" s="1" t="n"/>
@@ -5926,7 +5942,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>maa://21229 (84.69), maa://30807 (94.67), *maa://22767 (54.55), maa://42459 (91.89), ***maa://20796 (13.79)</t>
+          <t>maa://21229 (84.26), maa://30807 (93.42), *maa://22767 (54.55), maa://42459 (89.47), ***maa://20796 (13.79)</t>
         </is>
       </c>
       <c r="I45" s="1" t="n"/>
@@ -5958,7 +5974,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>**maa://39364 (46.3)</t>
+          <t>**maa://39364 (45.61)</t>
         </is>
       </c>
       <c r="U45" s="1" t="n"/>
@@ -5995,7 +6011,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>maa://35931 (92.49), maa://43901 (94.34)</t>
+          <t>maa://35931 (92.61), maa://43901 (94.55)</t>
         </is>
       </c>
       <c r="I46" s="1" t="n"/>
@@ -6031,6 +6047,22 @@
         </is>
       </c>
       <c r="U46" s="1" t="n"/>
+      <c r="AD46" s="1" t="inlineStr">
+        <is>
+          <t>蒂比</t>
+        </is>
+      </c>
+      <c r="AE46" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF46" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG46" s="1" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="3" t="n"/>
@@ -6043,12 +6075,12 @@
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>maa://27410 (96.84), maa://29661 (97.62), maa://28038 (84.62)</t>
+          <t>maa://27410 (96.88), maa://29661 (97.63), maa://28038 (84.62), maa://56236 (100.0)</t>
         </is>
       </c>
       <c r="I47" s="1" t="n"/>
@@ -6170,7 +6202,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>*maa://39643 (56.82)</t>
+          <t>*maa://39643 (56.52)</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n"/>
@@ -6257,7 +6289,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>maa://30769 (82.35)</t>
+          <t>maa://30769 (83.33)</t>
         </is>
       </c>
       <c r="I51" s="1" t="n"/>
@@ -6318,12 +6350,12 @@
       </c>
       <c r="O52" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>maa://59378 (100.0), maa://59394 (100.0)</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n"/>
@@ -6357,7 +6389,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>maa://32534 (94.99), **maa://32434 (33.33)</t>
+          <t>maa://32534 (95.09), **maa://32434 (33.33)</t>
         </is>
       </c>
       <c r="I53" s="1" t="n"/>
@@ -6377,6 +6409,22 @@
         </is>
       </c>
       <c r="Q53" s="1" t="n"/>
+      <c r="R53" s="1" t="inlineStr">
+        <is>
+          <t>Miss.Christine</t>
+        </is>
+      </c>
+      <c r="S53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U53" s="1" t="n"/>
     </row>
     <row r="54">
       <c r="F54" s="1" t="inlineStr">
@@ -6425,7 +6473,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>maa://32532 (93.09)</t>
+          <t>maa://32532 (93.3)</t>
         </is>
       </c>
       <c r="I55" s="1" t="n"/>
@@ -6461,7 +6509,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>maa://25176 (98.53), maa://56237 (100.0)</t>
+          <t>maa://25176 (98.59), maa://56237 (100.0)</t>
         </is>
       </c>
       <c r="I57" s="1" t="n"/>
@@ -6479,7 +6527,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>*maa://37964 (54.72)</t>
+          <t>*maa://37964 (55.36)</t>
         </is>
       </c>
       <c r="I58" s="1" t="n"/>
@@ -6497,7 +6545,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>maa://31270 (94.52), maa://27746 (82.91)</t>
+          <t>maa://31270 (94.63), maa://27746 (82.91)</t>
         </is>
       </c>
       <c r="I59" s="1" t="n"/>
@@ -6515,7 +6563,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>*maa://40438 (73.33)</t>
+          <t>*maa://40438 (74.36)</t>
         </is>
       </c>
       <c r="I60" s="1" t="n"/>
@@ -6551,7 +6599,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>maa://42981 (96.55), maa://43903 (100.0), maa://56228 (100.0)</t>
+          <t>maa://42981 (96.61), maa://43903 (100.0), maa://56228 (100.0)</t>
         </is>
       </c>
       <c r="I62" s="1" t="n"/>
@@ -6564,12 +6612,12 @@
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>maa://59534 (94.12)</t>
         </is>
       </c>
       <c r="I63" s="1" t="n"/>
@@ -6587,7 +6635,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>maa://44405 (86.49)</t>
+          <t>maa://44405 (86.84)</t>
         </is>
       </c>
       <c r="I64" s="1" t="n"/>
